--- a/tame_output/ON/bt/strategyON_20240321.xlsx
+++ b/tame_output/ON/bt/strategyON_20240321.xlsx
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-63.1%</t>
+          <t>-63.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-370.9%</t>
+          <t>-371.0%</t>
         </is>
       </c>
     </row>
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-151.5%</t>
+          <t>-151.6%</t>
         </is>
       </c>
     </row>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.2781997024955</v>
+        <v>3.278199702495499</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347057</v>
+        <v>3.299136146347056</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178245</v>
+        <v>3.315884374178244</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006534</v>
+        <v>3.305849539006533</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309425</v>
+        <v>3.311086391309424</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330524</v>
+        <v>3.300815818330523</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108641</v>
+        <v>3.305023265108642</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094118</v>
+        <v>3.374439043094119</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199288</v>
+        <v>3.405960511199289</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969596</v>
+        <v>3.424633354969597</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317618</v>
+        <v>3.447750501317619</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737172</v>
+        <v>3.503515506737173</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341315</v>
+        <v>3.503170282341316</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776678</v>
+        <v>3.500446096776679</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407493</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611696</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910628</v>
+        <v>3.499968163910629</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078596</v>
+        <v>3.490055666078597</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880267</v>
+        <v>3.485875018880268</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234392</v>
+        <v>3.480688917234393</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767395</v>
+        <v>3.492098065767396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792539</v>
+        <v>3.57367044979254</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628916</v>
+        <v>3.600034689628917</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410713</v>
+        <v>3.691568158410714</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -45458,10 +45458,10 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-2.09282521440779</v>
+        <v>-2.094544203188928</v>
       </c>
       <c r="E1909" t="n">
-        <v>2.247136248386659</v>
+        <v>2.246448652874204</v>
       </c>
       <c r="F1909" t="n">
         <v>1.210643015647853</v>

--- a/tame_output/ON/bt/strategyON_20240321.xlsx
+++ b/tame_output/ON/bt/strategyON_20240321.xlsx
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-63.2%</t>
+          <t>-64.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>101.9%</t>
+          <t>101.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>86.4%</t>
+          <t>84.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.8%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-56.4%</t>
+          <t>-59.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>84.2%</t>
+          <t>83.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1022,12 +1022,12 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>497.2%</t>
+          <t>496.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-371.0%</t>
+          <t>-398.6%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>49.6%</t>
+          <t>49.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>41.5%</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-151.6%</t>
+          <t>-162.6%</t>
         </is>
       </c>
     </row>
@@ -45458,10 +45458,10 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-2.094544203188928</v>
+        <v>-2.369976017975339</v>
       </c>
       <c r="E1909" t="n">
-        <v>2.246448652874204</v>
+        <v>2.13627592695964</v>
       </c>
       <c r="F1909" t="n">
         <v>1.210643015647853</v>

--- a/tame_output/ON/bt/strategyON_20240321.xlsx
+++ b/tame_output/ON/bt/strategyON_20240321.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>62.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1906</v>
+        <v>1907</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,17 +628,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-03-20</t>
+          <t>2024-03-21</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.9%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.5%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.8%</t>
+          <t>-15.5%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.7%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>5.2%</t>
+          <t>40.7%</t>
         </is>
       </c>
     </row>
@@ -758,26 +758,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>72.9%</t>
+          <t>70.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1906</v>
+        <v>1907</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-03-20</t>
+          <t>2024-03-21</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,25 +801,25 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>16.0%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2021-03-21</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2021-03-24</t>
+          <t>2024-03-21</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-11.3%</t>
+          <t>-14.3%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-3.4%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>-4.8%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-9.3%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-64.8%</t>
+          <t>-65.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>101.2%</t>
+          <t>101.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1906</v>
+        <v>1907</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,12 +944,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-03-20</t>
+          <t>2024-03-21</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>116.7%</t>
+          <t>118.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -973,11 +973,11 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-501.4%</t>
+          <t>-512.0%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-39.1%</t>
+          <t>-39.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-59.6%</t>
+          <t>-60.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>83.9%</t>
+          <t>84.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>496.1%</t>
+          <t>501.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>-1.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-398.6%</t>
+          <t>-409.2%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>49.2%</t>
+          <t>49.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1906</v>
+        <v>1907</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-03-20</t>
+          <t>2024-03-21</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>98.2%</t>
+          <t>98.3%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1131,11 +1131,11 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-201.0%</t>
+          <t>-205.2%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-30.2%</t>
+          <t>-30.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-19.3%</t>
+          <t>-17.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>88.3%</t>
+          <t>182.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-162.6%</t>
+          <t>-166.8%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-4.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1906</v>
+        <v>1907</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-03-20</t>
+          <t>2024-03-21</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.2%</t>
+          <t>99.4%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1289,11 +1289,11 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-281.3%</t>
+          <t>-291.9%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-24.4%</t>
+          <t>-25.1%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>48.4%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-152.7%</t>
+          <t>-156.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-102.9%</t>
+          <t>-113.5%</t>
         </is>
       </c>
     </row>
@@ -1390,26 +1390,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>83.5%</t>
+          <t>40.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>58.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1906</v>
+        <v>1907</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-03-20</t>
+          <t>2024-03-21</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>76.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>93.2%</t>
+          <t>93.7%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1447,11 +1447,11 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-169.2%</t>
+          <t>-175.5%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,32 +1466,32 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.0%</t>
+          <t>-21.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>78.7%</t>
+          <t>33.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>40.1%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.5%</t>
+          <t>-14.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-64.9%</t>
+          <t>-144.4%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1909"/>
+  <dimension ref="A1:G1910"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911639</v>
+        <v>3.233800325911638</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,22 +44141,22 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213495</v>
+        <v>3.223539378213494</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-1.568188060883165</v>
+        <v>-1.674149034544949</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.502711207820068</v>
+        <v>2.460326818355355</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.4753428892670392</v>
+        <v>0.369381915605255</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.415548590047305</v>
+        <v>3.351972005850235</v>
       </c>
     </row>
     <row r="1853">
@@ -44164,22 +44164,22 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416045</v>
+        <v>3.231167537416043</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-1.564851314374194</v>
+        <v>-1.670812288035978</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.512144656832226</v>
+        <v>2.469760267367512</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.4780349216860705</v>
+        <v>0.3720739480242863</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.425262559907293</v>
+        <v>3.361685975710222</v>
       </c>
     </row>
     <row r="1854">
@@ -44187,22 +44187,22 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382328</v>
+        <v>3.235981977382327</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-1.931562366040739</v>
+        <v>-2.037523339702523</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.366566628209339</v>
+        <v>2.324182238744626</v>
       </c>
       <c r="F1854" t="n">
-        <v>0.1113238700195249</v>
+        <v>0.005362896357740732</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.206342320951098</v>
+        <v>3.142765736754027</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-1.931993065089335</v>
+        <v>-2.037954038751119</v>
       </c>
       <c r="E1855" t="n">
-        <v>2.364936887402765</v>
+        <v>2.322552497938051</v>
       </c>
       <c r="F1855" t="n">
-        <v>0.1113238700195249</v>
+        <v>0.005362896357740732</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.204884859763961</v>
+        <v>3.141308275566891</v>
       </c>
     </row>
     <row r="1856">
@@ -44233,22 +44233,22 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347056</v>
+        <v>3.299136146347055</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-2.275675838315998</v>
+        <v>-2.381636811977782</v>
       </c>
       <c r="E1856" t="n">
-        <v>2.229232901566716</v>
+        <v>2.186848512102002</v>
       </c>
       <c r="F1856" t="n">
-        <v>0.003417817992306726</v>
+        <v>-0.1025431556694775</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.141910352002246</v>
+        <v>3.078333767805176</v>
       </c>
     </row>
     <row r="1857">
@@ -44256,22 +44256,22 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130019</v>
+        <v>3.287377576130018</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-2.633326188554346</v>
+        <v>-2.73928716221613</v>
       </c>
       <c r="E1857" t="n">
-        <v>2.082278820127634</v>
+        <v>2.039894430662921</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.3542325322460414</v>
+        <v>-0.4601935059078256</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.923426200515495</v>
+        <v>2.859849616318425</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-2.639987128776494</v>
+        <v>-2.745948102438278</v>
       </c>
       <c r="E1858" t="n">
-        <v>2.081387370739034</v>
+        <v>2.039002981274321</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.3542325322460414</v>
+        <v>-0.4601935059078256</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.925199127215755</v>
+        <v>2.861622543018684</v>
       </c>
     </row>
     <row r="1859">
@@ -44302,22 +44302,22 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207814</v>
+        <v>3.305316798207812</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-3.071792921926281</v>
+        <v>-3.177753895588066</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.894997940946524</v>
+        <v>1.85261355148181</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.4906500286873084</v>
+        <v>-0.5966110023490926</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.829681516818399</v>
+        <v>2.766104932621329</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310982</v>
+        <v>3.284619513310981</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-3.398225450794025</v>
+        <v>-3.504186424455809</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.752709704401517</v>
+        <v>1.710325314936803</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.5731182791944566</v>
+        <v>-0.6790792528562408</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.768485341516201</v>
+        <v>2.70490875731913</v>
       </c>
     </row>
     <row r="1861">
@@ -44348,22 +44348,22 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006533</v>
+        <v>3.305849539006532</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-3.399789601904328</v>
+        <v>-3.505750575566112</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.750664635613361</v>
+        <v>1.708280246148647</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.5731182791944566</v>
+        <v>-0.6790792528562408</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.767065933172166</v>
+        <v>2.703489348975095</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-3.763415846804641</v>
+        <v>-3.869376820466425</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.611701697887478</v>
+        <v>1.569317308422764</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.6713399160615824</v>
+        <v>-0.7773008897233666</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.714620511286132</v>
+        <v>2.651043927089062</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970906</v>
+        <v>3.304715716970905</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-3.760988782275922</v>
+        <v>-3.866949755937707</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.611927038704796</v>
+        <v>1.569542649240083</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.671672697868734</v>
+        <v>-0.7776336715305183</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.713675357207673</v>
+        <v>2.650098773010602</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-4.1695775594566</v>
+        <v>-4.275538533118386</v>
       </c>
       <c r="E1864" t="n">
-        <v>1.447253071847284</v>
+        <v>1.40486868238257</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.080261475049412</v>
+        <v>-1.186222448711197</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.467283634914025</v>
+        <v>2.403707050716954</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191739</v>
+        <v>3.302618194191738</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-4.582560043597694</v>
+        <v>-4.68852101725948</v>
       </c>
       <c r="E1865" t="n">
-        <v>1.277245510662307</v>
+        <v>1.234861121197593</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.080261475049412</v>
+        <v>-1.186222448711197</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.462469067385485</v>
+        <v>2.398892483188415</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108642</v>
+        <v>3.305023265108641</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-4.998951917884692</v>
+        <v>-5.104912891546477</v>
       </c>
       <c r="E1866" t="n">
-        <v>1.108682811556386</v>
+        <v>1.066298422091672</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.080261475049412</v>
+        <v>-1.186222448711197</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.460463117994363</v>
+        <v>2.396886533797292</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097823</v>
+        <v>3.341378723097822</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-5.375628928414536</v>
+        <v>-5.481589902076322</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.9682706980131268</v>
+        <v>0.9258863085484128</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.080261475049412</v>
+        <v>-1.186222448711197</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.470721808663042</v>
+        <v>2.407145224465971</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094119</v>
+        <v>3.374439043094118</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-5.389343792739647</v>
+        <v>-5.495304766401433</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.9588843174287778</v>
+        <v>0.9164999279640633</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.080261475049412</v>
+        <v>-1.186222448711197</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.466821373808737</v>
+        <v>2.403244789611666</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199289</v>
+        <v>3.405960511199288</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-5.702168591984627</v>
+        <v>-5.808129565646412</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.8321593177857869</v>
+        <v>0.7897749283210724</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.080261475049412</v>
+        <v>-1.186222448711197</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.465226293863738</v>
+        <v>2.401649709666667</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969597</v>
+        <v>3.424633354969596</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-5.706981630449964</v>
+        <v>-5.81294260411175</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.83401307832886</v>
+        <v>0.7916286888641459</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.081808109752198</v>
+        <v>-1.187769083413983</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.468077288971275</v>
+        <v>2.404500704774204</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-6.1403307385602</v>
+        <v>-6.246291712221986</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.6566471305503625</v>
+        <v>0.614262741085648</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.081808109752198</v>
+        <v>-1.187769083413983</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.464050984436871</v>
+        <v>2.4004744002398</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-6.523332127302831</v>
+        <v>-6.629293100964617</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.5033444737317261</v>
+        <v>0.4609600842670116</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.081808109752198</v>
+        <v>-1.187769083413983</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.463948883115287</v>
+        <v>2.400372298918216</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317619</v>
+        <v>3.447750501317618</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-6.898317453474109</v>
+        <v>-7.004278427135894</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.3559218592346451</v>
+        <v>0.3135374697699311</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.456793435923476</v>
+        <v>-1.56275440958526</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.241529203383951</v>
+        <v>2.17795261918688</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737173</v>
+        <v>3.503515506737171</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-7.25784777597811</v>
+        <v>-7.363808749639896</v>
       </c>
       <c r="E1874" t="n">
-        <v>0.2174600335310948</v>
+        <v>0.1750756440663803</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.456793435923476</v>
+        <v>-1.56275440958526</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.246879506682001</v>
+        <v>2.183302922484931</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341316</v>
+        <v>3.503170282341315</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-7.584247804643123</v>
+        <v>-7.690208778304909</v>
       </c>
       <c r="E1875" t="n">
-        <v>0.09481604202226679</v>
+        <v>0.05243165255755278</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.783193464588488</v>
+        <v>-1.889154438250273</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.058955509440171</v>
+        <v>1.9953789252431</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776679</v>
+        <v>3.500446096776678</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-7.577771657849564</v>
+        <v>-7.683732631511349</v>
       </c>
       <c r="E1876" t="n">
-        <v>0.1004482513614597</v>
+        <v>0.05806386189674528</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.776717317794929</v>
+        <v>-1.882678291456713</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.065882948138076</v>
+        <v>2.002306363941005</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-7.574080732893152</v>
+        <v>-7.680041706554937</v>
       </c>
       <c r="E1877" t="n">
-        <v>0.1019246213440241</v>
+        <v>0.05954023187931012</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.776717317794929</v>
+        <v>-1.882678291456713</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.065882948138076</v>
+        <v>2.002306363941005</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-7.566865380021336</v>
+        <v>-7.672826353683122</v>
       </c>
       <c r="E1878" t="n">
-        <v>0.1103239596113932</v>
+        <v>0.06793957014667873</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.706939082504547</v>
+        <v>-1.812900056166332</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.113263086430947</v>
+        <v>2.049686502233876</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-7.51583753393951</v>
+        <v>-7.621798507601295</v>
       </c>
       <c r="E1879" t="n">
-        <v>0.1352176525285596</v>
+        <v>0.09283326306384554</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.631729744197446</v>
+        <v>-1.73769071785923</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.162871243899644</v>
+        <v>2.099294659702573</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-7.442367702272062</v>
+        <v>-7.548328675933847</v>
       </c>
       <c r="E1880" t="n">
-        <v>0.1799772866889597</v>
+        <v>0.1375928972242457</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.558259912529997</v>
+        <v>-1.664220886191782</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.222324844393534</v>
+        <v>2.158748260196463</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-7.361995346808132</v>
+        <v>-7.467956320469917</v>
       </c>
       <c r="E1881" t="n">
-        <v>0.2266814496220486</v>
+        <v>0.1842970601573346</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.477887557066068</v>
+        <v>-1.583848530727852</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.285103478419408</v>
+        <v>2.221526894222338</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-7.550268149173976</v>
+        <v>-7.656229122835762</v>
       </c>
       <c r="E1882" t="n">
-        <v>0.1441531637741149</v>
+        <v>0.1017687743094009</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.477887557066068</v>
+        <v>-1.583848530727852</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.277884313517812</v>
+        <v>2.214307729320741</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-7.570432790723523</v>
+        <v>-7.676393764385309</v>
       </c>
       <c r="E1883" t="n">
-        <v>0.1294151163803199</v>
+        <v>0.08703072691560587</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.498052198615615</v>
+        <v>-1.6040131722774</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.259113337814108</v>
+        <v>2.195536753617037</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-7.800257237887348</v>
+        <v>-7.906218211549134</v>
       </c>
       <c r="E1884" t="n">
-        <v>0.03860112735334642</v>
+        <v>-0.003783262111368035</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.660699735685776</v>
+        <v>-1.76666070934756</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.162640605410568</v>
+        <v>2.099064021213497</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-7.737188005581009</v>
+        <v>-7.843148979242795</v>
       </c>
       <c r="E1885" t="n">
-        <v>0.06652254890499654</v>
+        <v>0.02413815944028253</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.68921329836801</v>
+        <v>-1.795174272029795</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.148226196430342</v>
+        <v>2.084649612233271</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-7.685172491612197</v>
+        <v>-7.791133465273982</v>
       </c>
       <c r="E1886" t="n">
-        <v>0.09131909017892248</v>
+        <v>0.04893470071420802</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.68921329836801</v>
+        <v>-1.795174272029795</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.152216532116743</v>
+        <v>2.088639947919672</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-7.766464421166401</v>
+        <v>-7.872425394828187</v>
       </c>
       <c r="E1887" t="n">
-        <v>0.0573270914584989</v>
+        <v>0.01494270199378445</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.68921329836801</v>
+        <v>-1.795174272029795</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.150741305218001</v>
+        <v>2.087164721020931</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-7.569195015438403</v>
+        <v>-7.675155989100189</v>
       </c>
       <c r="E1888" t="n">
-        <v>0.1512882639145703</v>
+        <v>0.1089038744498563</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.491943892640012</v>
+        <v>-1.597904866301796</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.284156358819672</v>
+        <v>2.220579774622601</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-7.370042908201304</v>
+        <v>-7.47600388186309</v>
       </c>
       <c r="E1889" t="n">
-        <v>0.2178979731627271</v>
+        <v>0.1755135836980126</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.326621366690198</v>
+        <v>-1.432582340351983</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.370298740742877</v>
+        <v>2.306722156545806</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-7.144197755481893</v>
+        <v>-7.250158729143679</v>
       </c>
       <c r="E1890" t="n">
-        <v>0.3178151072866999</v>
+        <v>0.2754307178219859</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.284694691103035</v>
+        <v>-1.390655664764819</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.405033819131384</v>
+        <v>2.341457234934313</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-6.857922943159199</v>
+        <v>-6.963883916820985</v>
       </c>
       <c r="E1891" t="n">
-        <v>0.4334641767718366</v>
+        <v>0.3910797873071226</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.284694691103035</v>
+        <v>-1.390655664764819</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.406172963687443</v>
+        <v>2.342596379490372</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-6.631127116085866</v>
+        <v>-6.737088089747651</v>
       </c>
       <c r="E1892" t="n">
-        <v>0.5268162817632778</v>
+        <v>0.4844318922985633</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.21658074648149</v>
+        <v>-1.322541720143275</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.449675104622477</v>
+        <v>2.386098520425406</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-6.347218385157117</v>
+        <v>-6.453179358818902</v>
       </c>
       <c r="E1893" t="n">
-        <v>0.6461134783734135</v>
+        <v>0.6037290889086995</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.21658074648149</v>
+        <v>-1.322541720143275</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.455408808861114</v>
+        <v>2.391832224664043</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-6.100231134964164</v>
+        <v>-6.20619210862595</v>
       </c>
       <c r="E1894" t="n">
-        <v>0.7351711160567294</v>
+        <v>0.6927867265920153</v>
       </c>
       <c r="F1894" t="n">
-        <v>-0.9695934962885383</v>
+        <v>-1.075554469950323</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.59386389658302</v>
+        <v>2.530287312385949</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702411</v>
+        <v>3.74769908470241</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-5.836394267760095</v>
+        <v>-5.942355241421881</v>
       </c>
       <c r="E1895" t="n">
-        <v>0.8308223816254494</v>
+        <v>0.7884379921607354</v>
       </c>
       <c r="F1895" t="n">
-        <v>-0.9695934962885383</v>
+        <v>-1.075554469950323</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.583980415270112</v>
+        <v>2.520403831073041</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-5.569152466891699</v>
+        <v>-5.675113440553484</v>
       </c>
       <c r="E1896" t="n">
-        <v>0.9358845414734347</v>
+        <v>0.8935001520087202</v>
       </c>
       <c r="F1896" t="n">
-        <v>-0.9695934962885383</v>
+        <v>-1.075554469950323</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.582145854770738</v>
+        <v>2.518569270573668</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-5.293343303491215</v>
+        <v>-5.399304277153</v>
       </c>
       <c r="E1897" t="n">
-        <v>1.045907891860167</v>
+        <v>1.003523502395453</v>
       </c>
       <c r="F1897" t="n">
-        <v>-0.8805741880098048</v>
+        <v>-0.9865351616715895</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.635257124764518</v>
+        <v>2.571680540567447</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-5.024275715724235</v>
+        <v>-5.13023668938602</v>
       </c>
       <c r="E1898" t="n">
-        <v>1.154203433112453</v>
+        <v>1.111819043647738</v>
       </c>
       <c r="F1898" t="n">
-        <v>-0.6115066002428254</v>
+        <v>-0.7174675739046101</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.797366183570199</v>
+        <v>2.733789599373128</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-4.760215777401439</v>
+        <v>-4.866176751063224</v>
       </c>
       <c r="E1899" t="n">
-        <v>1.246567092279819</v>
+        <v>1.204182702815105</v>
       </c>
       <c r="F1899" t="n">
-        <v>-0.3474466619200293</v>
+        <v>-0.453407635581814</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.942541830402125</v>
+        <v>2.878965246205054</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-4.053136153896601</v>
+        <v>-4.159097127558386</v>
       </c>
       <c r="E1900" t="n">
-        <v>1.526611908021454</v>
+        <v>1.484227518556739</v>
       </c>
       <c r="F1900" t="n">
-        <v>-0.3474466619200293</v>
+        <v>-0.453407635581814</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.939754796741824</v>
+        <v>2.876178212544753</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-3.803495123910649</v>
+        <v>-3.909456097572434</v>
       </c>
       <c r="E1901" t="n">
-        <v>1.626811943903676</v>
+        <v>1.584427554438961</v>
       </c>
       <c r="F1901" t="n">
-        <v>-0.09780563193407754</v>
+        <v>-0.2037666055958622</v>
       </c>
       <c r="G1901" t="n">
-        <v>3.089883038621236</v>
+        <v>3.026306454424165</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-3.548953224569573</v>
+        <v>-3.654914198231359</v>
       </c>
       <c r="E1902" t="n">
-        <v>1.727995524860863</v>
+        <v>1.685611135396148</v>
       </c>
       <c r="F1902" t="n">
-        <v>0.156736267406998</v>
+        <v>0.05077529374521328</v>
       </c>
       <c r="G1902" t="n">
-        <v>3.241974999446638</v>
+        <v>3.178398415249568</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761808</v>
+        <v>3.78732685376181</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-3.315472002339975</v>
+        <v>-3.42143297600176</v>
       </c>
       <c r="E1903" t="n">
-        <v>1.829312442590554</v>
+        <v>1.78692805312584</v>
       </c>
       <c r="F1903" t="n">
-        <v>0.3902174896365965</v>
+        <v>0.2842565159748118</v>
       </c>
       <c r="G1903" t="n">
-        <v>3.38998816162225</v>
+        <v>3.326411577425179</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255785</v>
+        <v>3.801633547255786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-3.135763472196102</v>
+        <v>-3.241724445857888</v>
       </c>
       <c r="E1904" t="n">
-        <v>1.898303644335144</v>
+        <v>1.85591925487043</v>
       </c>
       <c r="F1904" t="n">
-        <v>0.4473889937992926</v>
+        <v>0.3414280201375079</v>
       </c>
       <c r="G1904" t="n">
-        <v>3.421398853806908</v>
+        <v>3.357822269609838</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860426</v>
+        <v>3.763178672860428</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-3.003487998565215</v>
+        <v>-3.109448972227001</v>
       </c>
       <c r="E1905" t="n">
-        <v>1.946581320534526</v>
+        <v>1.904196931069812</v>
       </c>
       <c r="F1905" t="n">
-        <v>0.5796644674301793</v>
+        <v>0.4737034937683946</v>
       </c>
       <c r="G1905" t="n">
-        <v>3.496131624732467</v>
+        <v>3.432555040535397</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575951</v>
+        <v>3.784715218575952</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-2.812888323892063</v>
+        <v>-2.918849297553848</v>
       </c>
       <c r="E1906" t="n">
-        <v>2.025636251091424</v>
+        <v>1.98325186162671</v>
       </c>
       <c r="F1906" t="n">
-        <v>0.7702641421033322</v>
+        <v>0.6643031684415475</v>
       </c>
       <c r="G1906" t="n">
-        <v>3.613306490223996</v>
+        <v>3.549729906026925</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430984</v>
+        <v>3.753878996430986</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-2.563888525208482</v>
+        <v>-2.669849498870267</v>
       </c>
       <c r="E1907" t="n">
-        <v>2.138142511788515</v>
+        <v>2.095758122323801</v>
       </c>
       <c r="F1907" t="n">
-        <v>1.019263940786913</v>
+        <v>0.9133029671251282</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.775612710657803</v>
+        <v>3.712036126460732</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077641</v>
+        <v>3.692928280077643</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-2.372509450347542</v>
+        <v>-2.478470424009327</v>
       </c>
       <c r="E1908" t="n">
-        <v>2.086718212133672</v>
+        <v>2.044333822668958</v>
       </c>
       <c r="F1908" t="n">
-        <v>1.210643015647853</v>
+        <v>1.104682041986068</v>
       </c>
       <c r="G1908" t="n">
-        <v>3.762464225975148</v>
+        <v>3.698887641778077</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,45 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.332558016637874</v>
+        <v>3.770419008457901</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-2.369976017975339</v>
+        <v>-2.475936991637124</v>
       </c>
       <c r="E1909" t="n">
-        <v>2.13627592695964</v>
+        <v>2.093891537494926</v>
       </c>
       <c r="F1909" t="n">
-        <v>1.210643015647853</v>
+        <v>1.104682041986068</v>
       </c>
       <c r="G1909" t="n">
-        <v>3.811008567852235</v>
+        <v>3.747431983655164</v>
+      </c>
+    </row>
+    <row r="1910">
+      <c r="A1910" s="2" t="n">
+        <v>45372</v>
+      </c>
+      <c r="B1910" t="n">
+        <v>3.687551785469371</v>
+      </c>
+      <c r="C1910" t="n">
+        <v>3.022946375089586</v>
+      </c>
+      <c r="D1910" t="n">
+        <v>-2.475936991637124</v>
+      </c>
+      <c r="E1910" t="n">
+        <v>2.093891537494926</v>
+      </c>
+      <c r="F1910" t="n">
+        <v>1.104682041986068</v>
+      </c>
+      <c r="G1910" t="n">
+        <v>3.016010172075954</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240321.xlsx
+++ b/tame_output/ON/bt/strategyON_20240321.xlsx
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-65.9%</t>
+          <t>-64.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>101.9%</t>
+          <t>102.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>118.0%</t>
+          <t>118.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>84.8%</t>
+          <t>86.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-512.0%</t>
+          <t>-512.2%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>21.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-60.1%</t>
+          <t>-58.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>84.5%</t>
+          <t>85.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>501.0%</t>
+          <t>502.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-1.8%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-409.2%</t>
+          <t>-381.7%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>49.4%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-205.2%</t>
+          <t>-205.3%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>41.6%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-17.1%</t>
+          <t>-17.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>182.5%</t>
+          <t>188.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-166.8%</t>
+          <t>-155.9%</t>
         </is>
       </c>
     </row>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-291.9%</t>
+          <t>-292.1%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-156.9%</t>
+          <t>-157.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-113.5%</t>
+          <t>-113.7%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>40.4%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>76.2%</t>
+          <t>76.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-175.5%</t>
+          <t>-175.7%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.5%</t>
+          <t>-21.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>33.2%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911638</v>
+        <v>3.233800325911639</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-1.674149034544949</v>
+        <v>-1.67635774091149</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.460326818355355</v>
+        <v>2.459443335808738</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.369381915605255</v>
+        <v>0.3671732092387146</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.351972005850235</v>
+        <v>3.350646782030311</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-1.670812288035978</v>
+        <v>-1.673020994402518</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.469760267367512</v>
+        <v>2.468876784820896</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.3720739480242863</v>
+        <v>0.369865241657746</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.361685975710222</v>
+        <v>3.360360751890298</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.037523339702523</v>
+        <v>-2.039732046069064</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.324182238744626</v>
+        <v>2.32329875619801</v>
       </c>
       <c r="F1854" t="n">
-        <v>0.005362896357740732</v>
+        <v>0.003154189991200373</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.142765736754027</v>
+        <v>3.141440512934103</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-2.037954038751119</v>
+        <v>-2.04016274511766</v>
       </c>
       <c r="E1855" t="n">
-        <v>2.322552497938051</v>
+        <v>2.321669015391435</v>
       </c>
       <c r="F1855" t="n">
-        <v>0.005362896357740732</v>
+        <v>0.003154189991200373</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.141308275566891</v>
+        <v>3.139983051746966</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-2.381636811977782</v>
+        <v>-2.383845518344322</v>
       </c>
       <c r="E1856" t="n">
-        <v>2.186848512102002</v>
+        <v>2.185965029555386</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.1025431556694775</v>
+        <v>-0.1047518620360178</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.078333767805176</v>
+        <v>3.077008543985252</v>
       </c>
     </row>
     <row r="1857">
@@ -44256,22 +44256,22 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130018</v>
+        <v>3.287377576130017</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-2.73928716221613</v>
+        <v>-2.74149586858267</v>
       </c>
       <c r="E1857" t="n">
-        <v>2.039894430662921</v>
+        <v>2.039010948116305</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.4601935059078256</v>
+        <v>-0.462402212274366</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.859849616318425</v>
+        <v>2.8585243924985</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-2.745948102438278</v>
+        <v>-2.748156808804818</v>
       </c>
       <c r="E1858" t="n">
-        <v>2.039002981274321</v>
+        <v>2.038119498727705</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.4601935059078256</v>
+        <v>-0.462402212274366</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.861622543018684</v>
+        <v>2.86029731919876</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-3.177753895588066</v>
+        <v>-3.179962601954606</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.85261355148181</v>
+        <v>1.851730068935194</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.5966110023490926</v>
+        <v>-0.5988197087156329</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.766104932621329</v>
+        <v>2.764779708801405</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-3.504186424455809</v>
+        <v>-3.506395130822349</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.710325314936803</v>
+        <v>1.709441832390187</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.6790792528562408</v>
+        <v>-0.6812879592227812</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.70490875731913</v>
+        <v>2.703583533499206</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-3.505750575566112</v>
+        <v>-3.507959281932652</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.708280246148647</v>
+        <v>1.707396763602032</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.6790792528562408</v>
+        <v>-0.6812879592227812</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.703489348975095</v>
+        <v>2.702164125155171</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-3.869376820466425</v>
+        <v>-3.871585526832965</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.569317308422764</v>
+        <v>1.568433825876148</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.7773008897233666</v>
+        <v>-0.779509596089907</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.651043927089062</v>
+        <v>2.649718703269137</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-3.866949755937707</v>
+        <v>-3.869158462304247</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.569542649240083</v>
+        <v>1.568659166693467</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.7776336715305183</v>
+        <v>-0.7798423778970587</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.650098773010602</v>
+        <v>2.648773549190678</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-4.275538533118386</v>
+        <v>-4.277747239484926</v>
       </c>
       <c r="E1864" t="n">
-        <v>1.40486868238257</v>
+        <v>1.403985199835954</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.186222448711197</v>
+        <v>-1.188431155077737</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.403707050716954</v>
+        <v>2.40238182689703</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-4.68852101725948</v>
+        <v>-4.69072972362602</v>
       </c>
       <c r="E1865" t="n">
-        <v>1.234861121197593</v>
+        <v>1.233977638650977</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.186222448711197</v>
+        <v>-1.188431155077737</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.398892483188415</v>
+        <v>2.39756725936849</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-5.104912891546477</v>
+        <v>-5.107121597913017</v>
       </c>
       <c r="E1866" t="n">
-        <v>1.066298422091672</v>
+        <v>1.065414939545056</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.186222448711197</v>
+        <v>-1.188431155077737</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.396886533797292</v>
+        <v>2.395561309977368</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-5.481589902076322</v>
+        <v>-5.483798608442862</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.9258863085484128</v>
+        <v>0.9250028260017968</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.186222448711197</v>
+        <v>-1.188431155077737</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.407145224465971</v>
+        <v>2.405820000646047</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-5.495304766401433</v>
+        <v>-5.497513472767973</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.9164999279640633</v>
+        <v>0.9156164454174474</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.186222448711197</v>
+        <v>-1.188431155077737</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.403244789611666</v>
+        <v>2.401919565791742</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-5.808129565646412</v>
+        <v>-5.810338272012952</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.7897749283210724</v>
+        <v>0.7888914457744565</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.186222448711197</v>
+        <v>-1.188431155077737</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.401649709666667</v>
+        <v>2.400324485846743</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-5.81294260411175</v>
+        <v>-5.815151310478289</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.7916286888641459</v>
+        <v>0.79074520631753</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.187769083413983</v>
+        <v>-1.189977789780523</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.404500704774204</v>
+        <v>2.40317548095428</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-6.246291712221986</v>
+        <v>-6.248500418588526</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.614262741085648</v>
+        <v>0.6133792585390321</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.187769083413983</v>
+        <v>-1.189977789780523</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.4004744002398</v>
+        <v>2.399149176419876</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-6.629293100964617</v>
+        <v>-6.631501807331157</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.4609600842670116</v>
+        <v>0.4600766017203957</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.187769083413983</v>
+        <v>-1.189977789780523</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.400372298918216</v>
+        <v>2.399047075098292</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.004278427135894</v>
+        <v>-7.006487133502434</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.3135374697699311</v>
+        <v>0.3126539872233152</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.56275440958526</v>
+        <v>-1.5649631159518</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.17795261918688</v>
+        <v>2.176627395366956</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-7.363808749639896</v>
+        <v>-7.366017456006436</v>
       </c>
       <c r="E1874" t="n">
-        <v>0.1750756440663803</v>
+        <v>0.1741921615197644</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.56275440958526</v>
+        <v>-1.5649631159518</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.183302922484931</v>
+        <v>2.181977698665006</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341315</v>
+        <v>3.503170282341314</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-7.690208778304909</v>
+        <v>-7.692417484671449</v>
       </c>
       <c r="E1875" t="n">
-        <v>0.05243165255755278</v>
+        <v>0.05154817001093681</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.889154438250273</v>
+        <v>-1.891363144616813</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.9953789252431</v>
+        <v>1.994053701423176</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-7.683732631511349</v>
+        <v>-7.685941337877889</v>
       </c>
       <c r="E1876" t="n">
-        <v>0.05806386189674528</v>
+        <v>0.05718037935012932</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.882678291456713</v>
+        <v>-1.884886997823254</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.002306363941005</v>
+        <v>2.00098114012108</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-7.680041706554937</v>
+        <v>-7.682250412921477</v>
       </c>
       <c r="E1877" t="n">
-        <v>0.05954023187931012</v>
+        <v>0.05865674933269416</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.882678291456713</v>
+        <v>-1.884886997823254</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.002306363941005</v>
+        <v>2.00098114012108</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-7.672826353683122</v>
+        <v>-7.675035060049662</v>
       </c>
       <c r="E1878" t="n">
-        <v>0.06793957014667873</v>
+        <v>0.06705608760006276</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.812900056166332</v>
+        <v>-1.815108762532872</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.049686502233876</v>
+        <v>2.048361278413952</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-7.621798507601295</v>
+        <v>-7.624007213967835</v>
       </c>
       <c r="E1879" t="n">
-        <v>0.09283326306384554</v>
+        <v>0.09194978051722957</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.73769071785923</v>
+        <v>-1.739899424225771</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.099294659702573</v>
+        <v>2.097969435882649</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-7.548328675933847</v>
+        <v>-7.550537382300387</v>
       </c>
       <c r="E1880" t="n">
-        <v>0.1375928972242457</v>
+        <v>0.1367094146776298</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.664220886191782</v>
+        <v>-1.666429592558322</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.158748260196463</v>
+        <v>2.157423036376539</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-7.467956320469917</v>
+        <v>-7.470165026836457</v>
       </c>
       <c r="E1881" t="n">
-        <v>0.1842970601573346</v>
+        <v>0.1834135776107186</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.583848530727852</v>
+        <v>-1.586057237094393</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.221526894222338</v>
+        <v>2.220201670402413</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-7.656229122835762</v>
+        <v>-7.658437829202302</v>
       </c>
       <c r="E1882" t="n">
-        <v>0.1017687743094009</v>
+        <v>0.1008852917627849</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.583848530727852</v>
+        <v>-1.586057237094393</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.214307729320741</v>
+        <v>2.212982505500817</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-7.676393764385309</v>
+        <v>-7.678602470751849</v>
       </c>
       <c r="E1883" t="n">
-        <v>0.08703072691560587</v>
+        <v>0.08614724436898991</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.6040131722774</v>
+        <v>-1.60622187864394</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.195536753617037</v>
+        <v>2.194211529797113</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-7.906218211549134</v>
+        <v>-7.908426917915674</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.003783262111368035</v>
+        <v>-0.004666744657984001</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.76666070934756</v>
+        <v>-1.768869415714101</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.099064021213497</v>
+        <v>2.097738797393573</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-7.843148979242795</v>
+        <v>-7.845357685609335</v>
       </c>
       <c r="E1885" t="n">
-        <v>0.02413815944028253</v>
+        <v>0.02325467689366656</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.795174272029795</v>
+        <v>-1.797382978396335</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.084649612233271</v>
+        <v>2.083324388413347</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-7.791133465273982</v>
+        <v>-7.793342171640522</v>
       </c>
       <c r="E1886" t="n">
-        <v>0.04893470071420802</v>
+        <v>0.04805121816759206</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.795174272029795</v>
+        <v>-1.797382978396335</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.088639947919672</v>
+        <v>2.087314724099748</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-7.872425394828187</v>
+        <v>-7.874634101194727</v>
       </c>
       <c r="E1887" t="n">
-        <v>0.01494270199378445</v>
+        <v>0.01405921944716848</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.795174272029795</v>
+        <v>-1.797382978396335</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.087164721020931</v>
+        <v>2.085839497201006</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-7.675155989100189</v>
+        <v>-7.677364695466729</v>
       </c>
       <c r="E1888" t="n">
-        <v>0.1089038744498563</v>
+        <v>0.1080203919032403</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.597904866301796</v>
+        <v>-1.600113572668337</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.220579774622601</v>
+        <v>2.219254550802678</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-7.47600388186309</v>
+        <v>-7.47821258822963</v>
       </c>
       <c r="E1889" t="n">
-        <v>0.1755135836980126</v>
+        <v>0.1746301011513967</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.432582340351983</v>
+        <v>-1.434791046718523</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.306722156545806</v>
+        <v>2.305396932725882</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-7.250158729143679</v>
+        <v>-7.252367435510219</v>
       </c>
       <c r="E1890" t="n">
-        <v>0.2754307178219859</v>
+        <v>0.2745472352753699</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.390655664764819</v>
+        <v>-1.39286437113136</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.341457234934313</v>
+        <v>2.340132011114389</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282099</v>
+        <v>3.684840248282098</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-6.963883916820985</v>
+        <v>-6.966092623187524</v>
       </c>
       <c r="E1891" t="n">
-        <v>0.3910797873071226</v>
+        <v>0.3901963047605066</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.390655664764819</v>
+        <v>-1.39286437113136</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.342596379490372</v>
+        <v>2.341271155670448</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116214</v>
+        <v>3.710931958116213</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-6.737088089747651</v>
+        <v>-6.739296796114191</v>
       </c>
       <c r="E1892" t="n">
-        <v>0.4844318922985633</v>
+        <v>0.4835484097519474</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.322541720143275</v>
+        <v>-1.324750426509815</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.386098520425406</v>
+        <v>2.384773296605482</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081566</v>
+        <v>3.768948099081565</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-6.453179358818902</v>
+        <v>-6.455388065185442</v>
       </c>
       <c r="E1893" t="n">
-        <v>0.6037290889086995</v>
+        <v>0.6028456063620835</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.322541720143275</v>
+        <v>-1.324750426509815</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.391832224664043</v>
+        <v>2.390507000844119</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425326</v>
+        <v>3.728574354425325</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-6.20619210862595</v>
+        <v>-6.20840081499249</v>
       </c>
       <c r="E1894" t="n">
-        <v>0.6927867265920153</v>
+        <v>0.6919032440453994</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.075554469950323</v>
+        <v>-1.077763176316863</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.530287312385949</v>
+        <v>2.528962088566025</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.74769908470241</v>
+        <v>3.747699084702409</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-5.942355241421881</v>
+        <v>-5.944563947788421</v>
       </c>
       <c r="E1895" t="n">
-        <v>0.7884379921607354</v>
+        <v>0.7875545096141194</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.075554469950323</v>
+        <v>-1.077763176316863</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.520403831073041</v>
+        <v>2.519078607253117</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906227</v>
+        <v>3.766313503906225</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-5.675113440553484</v>
+        <v>-5.677322146920024</v>
       </c>
       <c r="E1896" t="n">
-        <v>0.8935001520087202</v>
+        <v>0.8926166694621043</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.075554469950323</v>
+        <v>-1.077763176316863</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.518569270573668</v>
+        <v>2.517244046753743</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781949</v>
+        <v>3.784680945781947</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-5.399304277153</v>
+        <v>-5.40151298351954</v>
       </c>
       <c r="E1897" t="n">
-        <v>1.003523502395453</v>
+        <v>1.002640019848837</v>
       </c>
       <c r="F1897" t="n">
-        <v>-0.9865351616715895</v>
+        <v>-0.9887438680381299</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.571680540567447</v>
+        <v>2.570355316747523</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567244</v>
+        <v>3.800825778567242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-5.13023668938602</v>
+        <v>-5.13244539575256</v>
       </c>
       <c r="E1898" t="n">
-        <v>1.111819043647738</v>
+        <v>1.110935561101122</v>
       </c>
       <c r="F1898" t="n">
-        <v>-0.7174675739046101</v>
+        <v>-0.7196762802711505</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.733789599373128</v>
+        <v>2.732464375553204</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487773</v>
+        <v>3.789307536487772</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-4.866176751063224</v>
+        <v>-4.868385457429764</v>
       </c>
       <c r="E1899" t="n">
-        <v>1.204182702815105</v>
+        <v>1.203299220268489</v>
       </c>
       <c r="F1899" t="n">
-        <v>-0.453407635581814</v>
+        <v>-0.4556163419483543</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.878965246205054</v>
+        <v>2.87764002238513</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309728</v>
+        <v>3.833249172309726</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-4.159097127558386</v>
+        <v>-4.161305833924926</v>
       </c>
       <c r="E1900" t="n">
-        <v>1.484227518556739</v>
+        <v>1.483344036010123</v>
       </c>
       <c r="F1900" t="n">
-        <v>-0.453407635581814</v>
+        <v>-0.4556163419483543</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.876178212544753</v>
+        <v>2.874852988724829</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.83937087185873</v>
+        <v>3.839370871858728</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-3.909456097572434</v>
+        <v>-3.911664803938974</v>
       </c>
       <c r="E1901" t="n">
-        <v>1.584427554438961</v>
+        <v>1.583544071892345</v>
       </c>
       <c r="F1901" t="n">
-        <v>-0.2037666055958622</v>
+        <v>-0.2059753119624026</v>
       </c>
       <c r="G1901" t="n">
-        <v>3.026306454424165</v>
+        <v>3.024981230604241</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096475</v>
+        <v>3.856158176096473</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-3.654914198231359</v>
+        <v>-3.657122904597899</v>
       </c>
       <c r="E1902" t="n">
-        <v>1.685611135396148</v>
+        <v>1.684727652849533</v>
       </c>
       <c r="F1902" t="n">
-        <v>0.05077529374521328</v>
+        <v>0.04856658737867292</v>
       </c>
       <c r="G1902" t="n">
-        <v>3.178398415249568</v>
+        <v>3.177073191429643</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.78732685376181</v>
+        <v>3.787326853761808</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-3.42143297600176</v>
+        <v>-3.4236416823683</v>
       </c>
       <c r="E1903" t="n">
-        <v>1.78692805312584</v>
+        <v>1.786044570579224</v>
       </c>
       <c r="F1903" t="n">
-        <v>0.2842565159748118</v>
+        <v>0.2820478096082715</v>
       </c>
       <c r="G1903" t="n">
-        <v>3.326411577425179</v>
+        <v>3.325086353605255</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255786</v>
+        <v>3.801633547255785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-3.241724445857888</v>
+        <v>-3.243933152224427</v>
       </c>
       <c r="E1904" t="n">
-        <v>1.85591925487043</v>
+        <v>1.855035772323814</v>
       </c>
       <c r="F1904" t="n">
-        <v>0.3414280201375079</v>
+        <v>0.3392193137709676</v>
       </c>
       <c r="G1904" t="n">
-        <v>3.357822269609838</v>
+        <v>3.356497045789913</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860428</v>
+        <v>3.763178672860426</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-3.109448972227001</v>
+        <v>-3.111657678593541</v>
       </c>
       <c r="E1905" t="n">
-        <v>1.904196931069812</v>
+        <v>1.903313448523196</v>
       </c>
       <c r="F1905" t="n">
-        <v>0.4737034937683946</v>
+        <v>0.4714947874018542</v>
       </c>
       <c r="G1905" t="n">
-        <v>3.432555040535397</v>
+        <v>3.431229816715472</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575952</v>
+        <v>3.784715218575951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-2.918849297553848</v>
+        <v>-2.921058003920388</v>
       </c>
       <c r="E1906" t="n">
-        <v>1.98325186162671</v>
+        <v>1.982368379080094</v>
       </c>
       <c r="F1906" t="n">
-        <v>0.6643031684415475</v>
+        <v>0.6620944620750071</v>
       </c>
       <c r="G1906" t="n">
-        <v>3.549729906026925</v>
+        <v>3.548404682207001</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430986</v>
+        <v>3.753878996430984</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-2.669849498870267</v>
+        <v>-2.672058205236807</v>
       </c>
       <c r="E1907" t="n">
-        <v>2.095758122323801</v>
+        <v>2.094874639777185</v>
       </c>
       <c r="F1907" t="n">
-        <v>0.9133029671251282</v>
+        <v>0.9110942607585878</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.712036126460732</v>
+        <v>3.710710902640808</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077643</v>
+        <v>3.692928280077641</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-2.478470424009327</v>
+        <v>-2.480679130375867</v>
       </c>
       <c r="E1908" t="n">
-        <v>2.044333822668958</v>
+        <v>2.043450340122342</v>
       </c>
       <c r="F1908" t="n">
-        <v>1.104682041986068</v>
+        <v>1.102473335619528</v>
       </c>
       <c r="G1908" t="n">
-        <v>3.698887641778077</v>
+        <v>3.697562417958153</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457901</v>
+        <v>3.770419008457899</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-2.475936991637124</v>
+        <v>-2.201651834720241</v>
       </c>
       <c r="E1909" t="n">
-        <v>2.093891537494926</v>
+        <v>2.203605600261679</v>
       </c>
       <c r="F1909" t="n">
-        <v>1.104682041986068</v>
+        <v>1.102473335619528</v>
       </c>
       <c r="G1909" t="n">
-        <v>3.747431983655164</v>
+        <v>3.74610675983524</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,19 +45475,19 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.687551785469371</v>
+        <v>3.687551785469369</v>
       </c>
       <c r="C1910" t="n">
         <v>3.022946375089586</v>
       </c>
       <c r="D1910" t="n">
-        <v>-2.475936991637124</v>
+        <v>-2.201651834720241</v>
       </c>
       <c r="E1910" t="n">
-        <v>2.093891537494926</v>
+        <v>2.203605600261679</v>
       </c>
       <c r="F1910" t="n">
-        <v>1.104682041986068</v>
+        <v>1.102473335619528</v>
       </c>
       <c r="G1910" t="n">
         <v>3.016010172075954</v>

--- a/tame_output/ON/bt/strategyON_20240321.xlsx
+++ b/tame_output/ON/bt/strategyON_20240321.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>49.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>69.8%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.5%</t>
+          <t>-17.8%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-12.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>8.8%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>70.8%</t>
+          <t>61.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>37.4%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>38.4%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-14.3%</t>
+          <t>-39.3%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,37 +839,37 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-6.0%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>24.8%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.8%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-9.3%</t>
+          <t>-34.3%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-64.3%</t>
+          <t>-65.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>102.7%</t>
+          <t>102.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>86.4%</t>
+          <t>86.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.8%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-58.5%</t>
+          <t>-61.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>85.2%</t>
+          <t>85.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>502.0%</t>
+          <t>497.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>-1.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-381.7%</t>
+          <t>-402.2%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>49.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-17.6%</t>
+          <t>-18.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>188.1%</t>
+          <t>152.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-155.9%</t>
+          <t>-164.1%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-4.8%</t>
+          <t>-6.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-157.0%</t>
+          <t>-156.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-113.7%</t>
+          <t>-121.0%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>5.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>76.1%</t>
+          <t>85.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>93.7%</t>
+          <t>98.0%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1443,11 +1443,11 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-03-21</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1476,37 +1476,37 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>48.4%</t>
+          <t>51.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
         <is>
           <t>0.1</t>
         </is>
       </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.5%</t>
+          <t>-13.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-144.4%</t>
+          <t>-169.4%</t>
         </is>
       </c>
     </row>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416043</v>
+        <v>3.231167537416044</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382327</v>
+        <v>3.235981977382328</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347055</v>
+        <v>3.299136146347056</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130017</v>
+        <v>3.287377576130019</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207812</v>
+        <v>3.305316798207813</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006532</v>
+        <v>3.305849539006533</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970905</v>
+        <v>3.304715716970906</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191738</v>
+        <v>3.302618194191739</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108641</v>
+        <v>3.305023265108642</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097822</v>
+        <v>3.341378723097823</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094118</v>
+        <v>3.374439043094119</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199288</v>
+        <v>3.405960511199289</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969596</v>
+        <v>3.424633354969597</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317618</v>
+        <v>3.447750501317619</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737171</v>
+        <v>3.503515506737172</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341314</v>
+        <v>3.503170282341316</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776678</v>
+        <v>3.500446096776679</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407495</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199886</v>
+        <v>3.496848329199887</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910629</v>
+        <v>3.49996816391063</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078597</v>
+        <v>3.490055666078598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880268</v>
+        <v>3.485875018880269</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234393</v>
+        <v>3.480688917234394</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860582</v>
+        <v>3.493712438860583</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767396</v>
+        <v>3.492098065767397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.57367044979254</v>
+        <v>3.573670449792541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628917</v>
+        <v>3.600034689628918</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410714</v>
+        <v>3.691568158410715</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240574</v>
+        <v>3.676837974240575</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-7.252367435510219</v>
+        <v>-7.548488871256496</v>
       </c>
       <c r="E1890" t="n">
-        <v>0.2745472352753699</v>
+        <v>0.1560986609768586</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.39286437113136</v>
+        <v>-1.465505102933976</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.340132011114389</v>
+        <v>2.296547572032819</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282098</v>
+        <v>3.684840248282099</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-6.966092623187524</v>
+        <v>-7.262214058933802</v>
       </c>
       <c r="E1891" t="n">
-        <v>0.3901963047605066</v>
+        <v>0.2717477304619953</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.39286437113136</v>
+        <v>-1.465505102933976</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.341271155670448</v>
+        <v>2.297686716588878</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116213</v>
+        <v>3.710931958116214</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-6.739296796114191</v>
+        <v>-7.035418231860469</v>
       </c>
       <c r="E1892" t="n">
-        <v>0.4835484097519474</v>
+        <v>0.3650998354534365</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.324750426509815</v>
+        <v>-1.397391158312431</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.384773296605482</v>
+        <v>2.341188857523913</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081565</v>
+        <v>3.768948099081566</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-6.455388065185442</v>
+        <v>-6.75150950093172</v>
       </c>
       <c r="E1893" t="n">
-        <v>0.6028456063620835</v>
+        <v>0.4843970320635727</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.324750426509815</v>
+        <v>-1.397391158312431</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.390507000844119</v>
+        <v>2.346922561762549</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425325</v>
+        <v>3.728574354425326</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-6.20840081499249</v>
+        <v>-6.504522250738767</v>
       </c>
       <c r="E1894" t="n">
-        <v>0.6919032440453994</v>
+        <v>0.5734546697468881</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.077763176316863</v>
+        <v>-1.150403908119479</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.528962088566025</v>
+        <v>2.485377649484455</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702409</v>
+        <v>3.74769908470241</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-5.944563947788421</v>
+        <v>-6.240685383534698</v>
       </c>
       <c r="E1895" t="n">
-        <v>0.7875545096141194</v>
+        <v>0.6691059353156081</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.077763176316863</v>
+        <v>-1.150403908119479</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.519078607253117</v>
+        <v>2.475494168171548</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906225</v>
+        <v>3.766313503906227</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-5.677322146920024</v>
+        <v>-5.973443582666301</v>
       </c>
       <c r="E1896" t="n">
-        <v>0.8926166694621043</v>
+        <v>0.7741680951635934</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.077763176316863</v>
+        <v>-1.150403908119479</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.517244046753743</v>
+        <v>2.473659607672174</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781947</v>
+        <v>3.784680945781949</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-5.40151298351954</v>
+        <v>-5.697634419265817</v>
       </c>
       <c r="E1897" t="n">
-        <v>1.002640019848837</v>
+        <v>0.8841914455503259</v>
       </c>
       <c r="F1897" t="n">
-        <v>-0.9887438680381299</v>
+        <v>-1.061384599840746</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.570355316747523</v>
+        <v>2.526770877665953</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567242</v>
+        <v>3.800825778567244</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-5.13244539575256</v>
+        <v>-5.428566831498838</v>
       </c>
       <c r="E1898" t="n">
-        <v>1.110935561101122</v>
+        <v>0.9924869868026116</v>
       </c>
       <c r="F1898" t="n">
-        <v>-0.7196762802711505</v>
+        <v>-0.7923170120737665</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.732464375553204</v>
+        <v>2.688879936471634</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487772</v>
+        <v>3.789307536487773</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-4.868385457429764</v>
+        <v>-5.164506893176042</v>
       </c>
       <c r="E1899" t="n">
-        <v>1.203299220268489</v>
+        <v>1.084850645969978</v>
       </c>
       <c r="F1899" t="n">
-        <v>-0.4556163419483543</v>
+        <v>-0.5282570737509703</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.87764002238513</v>
+        <v>2.83405558330356</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309726</v>
+        <v>3.833249172309728</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-4.161305833924926</v>
+        <v>-4.457427269671204</v>
       </c>
       <c r="E1900" t="n">
-        <v>1.483344036010123</v>
+        <v>1.364895461711612</v>
       </c>
       <c r="F1900" t="n">
-        <v>-0.4556163419483543</v>
+        <v>-0.5282570737509703</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.874852988724829</v>
+        <v>2.831268549643259</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858728</v>
+        <v>3.83937087185873</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-3.911664803938974</v>
+        <v>-4.207786239685252</v>
       </c>
       <c r="E1901" t="n">
-        <v>1.583544071892345</v>
+        <v>1.465095497593834</v>
       </c>
       <c r="F1901" t="n">
-        <v>-0.2059753119624026</v>
+        <v>-0.2786160437650186</v>
       </c>
       <c r="G1901" t="n">
-        <v>3.024981230604241</v>
+        <v>2.981396791522672</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096473</v>
+        <v>3.856158176096475</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-3.657122904597899</v>
+        <v>-3.953244340344176</v>
       </c>
       <c r="E1902" t="n">
-        <v>1.684727652849533</v>
+        <v>1.566279078551021</v>
       </c>
       <c r="F1902" t="n">
-        <v>0.04856658737867292</v>
+        <v>-0.02407414442394307</v>
       </c>
       <c r="G1902" t="n">
-        <v>3.177073191429643</v>
+        <v>3.133488752348074</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761808</v>
+        <v>3.78732685376181</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-3.4236416823683</v>
+        <v>-3.719763118114578</v>
       </c>
       <c r="E1903" t="n">
-        <v>1.786044570579224</v>
+        <v>1.667595996280713</v>
       </c>
       <c r="F1903" t="n">
-        <v>0.2820478096082715</v>
+        <v>0.2094070778056555</v>
       </c>
       <c r="G1903" t="n">
-        <v>3.325086353605255</v>
+        <v>3.281501914523685</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255785</v>
+        <v>3.801633547255786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-3.243933152224427</v>
+        <v>-3.540054587970705</v>
       </c>
       <c r="E1904" t="n">
-        <v>1.855035772323814</v>
+        <v>1.736587198025303</v>
       </c>
       <c r="F1904" t="n">
-        <v>0.3392193137709676</v>
+        <v>0.2665785819683516</v>
       </c>
       <c r="G1904" t="n">
-        <v>3.356497045789913</v>
+        <v>3.312912606708344</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860426</v>
+        <v>3.763178672860428</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-3.111657678593541</v>
+        <v>-3.407779114339818</v>
       </c>
       <c r="E1905" t="n">
-        <v>1.903313448523196</v>
+        <v>1.784864874224685</v>
       </c>
       <c r="F1905" t="n">
-        <v>0.4714947874018542</v>
+        <v>0.3988540555992383</v>
       </c>
       <c r="G1905" t="n">
-        <v>3.431229816715472</v>
+        <v>3.387645377633903</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575951</v>
+        <v>3.784715218575952</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-2.921058003920388</v>
+        <v>-3.217179439666666</v>
       </c>
       <c r="E1906" t="n">
-        <v>1.982368379080094</v>
+        <v>1.863919804781583</v>
       </c>
       <c r="F1906" t="n">
-        <v>0.6620944620750071</v>
+        <v>0.5894537302723911</v>
       </c>
       <c r="G1906" t="n">
-        <v>3.548404682207001</v>
+        <v>3.504820243125431</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430984</v>
+        <v>3.753878996430986</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-2.672058205236807</v>
+        <v>-2.968179640983085</v>
       </c>
       <c r="E1907" t="n">
-        <v>2.094874639777185</v>
+        <v>1.976426065478674</v>
       </c>
       <c r="F1907" t="n">
-        <v>0.9110942607585878</v>
+        <v>0.8384535289559718</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.710710902640808</v>
+        <v>3.667126463559238</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077641</v>
+        <v>3.692928280077643</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-2.480679130375867</v>
+        <v>-2.776800566122145</v>
       </c>
       <c r="E1908" t="n">
-        <v>2.043450340122342</v>
+        <v>1.925001765823831</v>
       </c>
       <c r="F1908" t="n">
-        <v>1.102473335619528</v>
+        <v>1.029832603816912</v>
       </c>
       <c r="G1908" t="n">
-        <v>3.697562417958153</v>
+        <v>3.653977978876584</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457899</v>
+        <v>3.770419008457901</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-2.201651834720241</v>
+        <v>-2.40657002664204</v>
       </c>
       <c r="E1909" t="n">
-        <v>2.203605600261679</v>
+        <v>2.121638323492959</v>
       </c>
       <c r="F1909" t="n">
-        <v>1.102473335619528</v>
+        <v>1.029832603816912</v>
       </c>
       <c r="G1909" t="n">
-        <v>3.74610675983524</v>
+        <v>3.70252232075367</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.687551785469369</v>
+        <v>3.368992457256376</v>
       </c>
       <c r="C1910" t="n">
-        <v>3.022946375089586</v>
+        <v>2.773280772463557</v>
       </c>
       <c r="D1910" t="n">
-        <v>-2.201651834720241</v>
+        <v>-2.40657002664204</v>
       </c>
       <c r="E1910" t="n">
-        <v>2.203605600261679</v>
+        <v>2.121638323492959</v>
       </c>
       <c r="F1910" t="n">
-        <v>1.102473335619528</v>
+        <v>1.029832603816912</v>
       </c>
       <c r="G1910" t="n">
-        <v>3.016010172075954</v>
+        <v>2.766344569449925</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240321.xlsx
+++ b/tame_output/ON/bt/strategyON_20240321.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>49.2%</t>
+          <t>49.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>9.1%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-65.7%</t>
+          <t>-66.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>102.8%</t>
+          <t>103.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>118.1%</t>
+          <t>119.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>86.6%</t>
+          <t>86.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-512.2%</t>
+          <t>-545.0%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>21.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-39.5%</t>
+          <t>-40.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-61.0%</t>
+          <t>-62.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>85.3%</t>
+          <t>86.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>497.3%</t>
+          <t>497.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-1.4%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-402.2%</t>
+          <t>-414.5%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>30.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>98.3%</t>
+          <t>98.5%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-205.3%</t>
+          <t>-218.4%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-30.5%</t>
+          <t>-31.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>41.6%</t>
+          <t>41.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-18.5%</t>
+          <t>-32.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>152.4%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-164.1%</t>
+          <t>-169.0%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-6.1%</t>
+          <t>-3.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.4%</t>
+          <t>99.3%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-292.1%</t>
+          <t>-290.3%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-25.1%</t>
+          <t>-25.0%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>4.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-121.0%</t>
+          <t>-111.9%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>-25.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>64.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>85.9%</t>
+          <t>88.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>98.0%</t>
+          <t>99.7%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-175.7%</t>
+          <t>-174.6%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.6%</t>
+          <t>-21.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>-1.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>51.8%</t>
+          <t>52.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-13.7%</t>
+          <t>-13.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -44141,22 +44141,22 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213494</v>
+        <v>3.223539378213495</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-1.67635774091149</v>
+        <v>-1.568188060883165</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.459443335808738</v>
+        <v>2.502711207820068</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.3671732092387146</v>
+        <v>0.4753428892670392</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.350646782030311</v>
+        <v>3.415548590047305</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-1.673020994402518</v>
+        <v>-2.000775297247001</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.468876784820896</v>
+        <v>2.337775063683103</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.369865241657746</v>
+        <v>0.3882061254645299</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.360360751890298</v>
+        <v>3.371365282174369</v>
       </c>
     </row>
     <row r="1854">
@@ -44187,22 +44187,22 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382328</v>
+        <v>3.235981977382327</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.039732046069064</v>
+        <v>-2.367486348913546</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.32329875619801</v>
+        <v>2.192197035060217</v>
       </c>
       <c r="F1854" t="n">
-        <v>0.003154189991200373</v>
+        <v>0.02149507379798427</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.141440512934103</v>
+        <v>3.152445043218174</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-2.04016274511766</v>
+        <v>-2.367917047962142</v>
       </c>
       <c r="E1855" t="n">
-        <v>2.321669015391435</v>
+        <v>2.190567294253642</v>
       </c>
       <c r="F1855" t="n">
-        <v>0.003154189991200373</v>
+        <v>0.02149507379798427</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.139983051746966</v>
+        <v>3.150987582031037</v>
       </c>
     </row>
     <row r="1856">
@@ -44233,22 +44233,22 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347056</v>
+        <v>3.299136146347055</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-2.383845518344322</v>
+        <v>-2.711599821188805</v>
       </c>
       <c r="E1856" t="n">
-        <v>2.185965029555386</v>
+        <v>2.054863308417593</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.1047518620360178</v>
+        <v>-0.08641097822923394</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.077008543985252</v>
+        <v>3.088013074269322</v>
       </c>
     </row>
     <row r="1857">
@@ -44256,22 +44256,22 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130019</v>
+        <v>3.287377576130018</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-2.74149586858267</v>
+        <v>-3.069250171427153</v>
       </c>
       <c r="E1857" t="n">
-        <v>2.039010948116305</v>
+        <v>1.907909226978512</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.462402212274366</v>
+        <v>-0.4440613284675821</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.8585243924985</v>
+        <v>2.869528922782571</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-2.748156808804818</v>
+        <v>-3.075911111649301</v>
       </c>
       <c r="E1858" t="n">
-        <v>2.038119498727705</v>
+        <v>1.907017777589912</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.462402212274366</v>
+        <v>-0.4440613284675821</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.86029731919876</v>
+        <v>2.871301849482831</v>
       </c>
     </row>
     <row r="1859">
@@ -44302,22 +44302,22 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207813</v>
+        <v>3.305316798207812</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-3.179962601954606</v>
+        <v>-3.507716904799088</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.851730068935194</v>
+        <v>1.720628347797401</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.5988197087156329</v>
+        <v>-0.5804788249088491</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.764779708801405</v>
+        <v>2.775784239085475</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-3.506395130822349</v>
+        <v>-3.834149433666832</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.709441832390187</v>
+        <v>1.578340111252394</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.6812879592227812</v>
+        <v>-0.6629470754159972</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.703583533499206</v>
+        <v>2.714588063783276</v>
       </c>
     </row>
     <row r="1861">
@@ -44348,22 +44348,22 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006533</v>
+        <v>3.305849539006532</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-3.507959281932652</v>
+        <v>-3.835713584777135</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.707396763602032</v>
+        <v>1.576295042464238</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.6812879592227812</v>
+        <v>-0.6629470754159972</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.702164125155171</v>
+        <v>2.713168655439242</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-3.871585526832965</v>
+        <v>-4.199339829677448</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.568433825876148</v>
+        <v>1.437332104738355</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.779509596089907</v>
+        <v>-0.761168712283123</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.649718703269137</v>
+        <v>2.660723233553208</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970906</v>
+        <v>3.304715716970905</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-3.869158462304247</v>
+        <v>-4.196912765148729</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.568659166693467</v>
+        <v>1.437557445555674</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.7798423778970587</v>
+        <v>-0.7615014940902747</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.648773549190678</v>
+        <v>2.659778079474748</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-4.277747239484926</v>
+        <v>-4.605501542329408</v>
       </c>
       <c r="E1864" t="n">
-        <v>1.403985199835954</v>
+        <v>1.272883478698161</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.188431155077737</v>
+        <v>-1.170090271270953</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.40238182689703</v>
+        <v>2.4133863571811</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191739</v>
+        <v>3.302618194191738</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-4.69072972362602</v>
+        <v>-5.018484026470502</v>
       </c>
       <c r="E1865" t="n">
-        <v>1.233977638650977</v>
+        <v>1.102875917513184</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.188431155077737</v>
+        <v>-1.170090271270953</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.39756725936849</v>
+        <v>2.40857178965256</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108642</v>
+        <v>3.305023265108641</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-5.107121597913017</v>
+        <v>-5.4348759007575</v>
       </c>
       <c r="E1866" t="n">
-        <v>1.065414939545056</v>
+        <v>0.9343132184072624</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.188431155077737</v>
+        <v>-1.170090271270953</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.395561309977368</v>
+        <v>2.406565840261438</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097823</v>
+        <v>3.341378723097822</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-5.483798608442862</v>
+        <v>-5.811552911287344</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.9250028260017968</v>
+        <v>0.7939011048640037</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.188431155077737</v>
+        <v>-1.170090271270953</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.405820000646047</v>
+        <v>2.416824530930117</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094119</v>
+        <v>3.374439043094118</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-5.497513472767973</v>
+        <v>-5.825267775612455</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.9156164454174474</v>
+        <v>0.7845147242796546</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.188431155077737</v>
+        <v>-1.170090271270953</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.401919565791742</v>
+        <v>2.412924096075812</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199289</v>
+        <v>3.405960511199288</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-5.810338272012952</v>
+        <v>-6.138092574857435</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.7888914457744565</v>
+        <v>0.6577897246366633</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.188431155077737</v>
+        <v>-1.170090271270953</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.400324485846743</v>
+        <v>2.411329016130813</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969597</v>
+        <v>3.424633354969596</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-5.815151310478289</v>
+        <v>-6.142905613322772</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.79074520631753</v>
+        <v>0.6596434851797368</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.189977789780523</v>
+        <v>-1.171636905973739</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.40317548095428</v>
+        <v>2.41418001123835</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-6.248500418588526</v>
+        <v>-6.576254721433008</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.6133792585390321</v>
+        <v>0.4822775374012394</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.189977789780523</v>
+        <v>-1.171636905973739</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.399149176419876</v>
+        <v>2.410153706703947</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-6.631501807331157</v>
+        <v>-6.959256110175639</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.4600766017203957</v>
+        <v>0.3289748805826029</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.189977789780523</v>
+        <v>-1.171636905973739</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.399047075098292</v>
+        <v>2.410051605382363</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317619</v>
+        <v>3.447750501317618</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.006487133502434</v>
+        <v>-7.334241436346916</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.3126539872233152</v>
+        <v>0.181552266085522</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.5649631159518</v>
+        <v>-1.546622232145016</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.176627395366956</v>
+        <v>2.187631925651027</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737172</v>
+        <v>3.503515506737171</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-7.366017456006436</v>
+        <v>-7.693771758850918</v>
       </c>
       <c r="E1874" t="n">
-        <v>0.1741921615197644</v>
+        <v>0.04309044038197163</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.5649631159518</v>
+        <v>-1.546622232145016</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.181977698665006</v>
+        <v>2.192982228949076</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341316</v>
+        <v>3.503170282341315</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-7.692417484671449</v>
+        <v>-8.020171787515931</v>
       </c>
       <c r="E1875" t="n">
-        <v>0.05154817001093681</v>
+        <v>-0.07955355112685636</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.891363144616813</v>
+        <v>-1.873022260810029</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.994053701423176</v>
+        <v>2.005058231707246</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776679</v>
+        <v>3.500446096776678</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-7.685941337877889</v>
+        <v>-8.013695640722371</v>
       </c>
       <c r="E1876" t="n">
-        <v>0.05718037935012932</v>
+        <v>-0.07392134178766341</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.884886997823254</v>
+        <v>-1.86654611401647</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.00098114012108</v>
+        <v>2.011985670405151</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407495</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-7.682250412921477</v>
+        <v>-8.010004715765961</v>
       </c>
       <c r="E1877" t="n">
-        <v>0.05865674933269416</v>
+        <v>-0.07244497180509901</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.884886997823254</v>
+        <v>-1.86654611401647</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.00098114012108</v>
+        <v>2.011985670405151</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-7.675035060049662</v>
+        <v>-8.002789362894145</v>
       </c>
       <c r="E1878" t="n">
-        <v>0.06705608760006276</v>
+        <v>-0.06404563353773041</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.815108762532872</v>
+        <v>-1.796767878726088</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.048361278413952</v>
+        <v>2.059365808698022</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199887</v>
+        <v>3.496848329199886</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-7.624007213967835</v>
+        <v>-7.951761516812319</v>
       </c>
       <c r="E1879" t="n">
-        <v>0.09194978051722957</v>
+        <v>-0.03915194062056404</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.739899424225771</v>
+        <v>-1.721558540418987</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.097969435882649</v>
+        <v>2.108973966166719</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.49996816391063</v>
+        <v>3.499968163910629</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-7.550537382300387</v>
+        <v>-7.878291685144871</v>
       </c>
       <c r="E1880" t="n">
-        <v>0.1367094146776298</v>
+        <v>0.005607693539836589</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.666429592558322</v>
+        <v>-1.648088708751538</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.157423036376539</v>
+        <v>2.168427566660609</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078598</v>
+        <v>3.490055666078597</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-7.470165026836457</v>
+        <v>-7.797919329680941</v>
       </c>
       <c r="E1881" t="n">
-        <v>0.1834135776107186</v>
+        <v>0.05231185647292502</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.586057237094393</v>
+        <v>-1.567716353287609</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.220201670402413</v>
+        <v>2.231206200686484</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880269</v>
+        <v>3.485875018880268</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-7.658437829202302</v>
+        <v>-7.986192132046785</v>
       </c>
       <c r="E1882" t="n">
-        <v>0.1008852917627849</v>
+        <v>-0.03021642937500868</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.586057237094393</v>
+        <v>-1.567716353287609</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.212982505500817</v>
+        <v>2.223987035784888</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234394</v>
+        <v>3.480688917234393</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-7.678602470751849</v>
+        <v>-8.006356773596332</v>
       </c>
       <c r="E1883" t="n">
-        <v>0.08614724436898991</v>
+        <v>-0.04495447676880371</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.60622187864394</v>
+        <v>-1.587880994837156</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.194211529797113</v>
+        <v>2.205216060081183</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860583</v>
+        <v>3.493712438860582</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-7.908426917915674</v>
+        <v>-8.236181220760157</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.004666744657984001</v>
+        <v>-0.1357684657957772</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.768869415714101</v>
+        <v>-1.750528531907316</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.097738797393573</v>
+        <v>2.108743327677643</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767397</v>
+        <v>3.492098065767396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-7.845357685609335</v>
+        <v>-8.173111988453817</v>
       </c>
       <c r="E1885" t="n">
-        <v>0.02325467689366656</v>
+        <v>-0.1078470442441266</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.797382978396335</v>
+        <v>-1.779042094589551</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.083324388413347</v>
+        <v>2.094328918697418</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792541</v>
+        <v>3.57367044979254</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-7.793342171640522</v>
+        <v>-8.121096474485004</v>
       </c>
       <c r="E1886" t="n">
-        <v>0.04805121816759206</v>
+        <v>-0.08305050297020067</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.797382978396335</v>
+        <v>-1.779042094589551</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.087314724099748</v>
+        <v>2.098319254383818</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628918</v>
+        <v>3.600034689628917</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-7.874634101194727</v>
+        <v>-8.202388404039208</v>
       </c>
       <c r="E1887" t="n">
-        <v>0.01405921944716848</v>
+        <v>-0.1170425016906238</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.797382978396335</v>
+        <v>-1.779042094589551</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.085839497201006</v>
+        <v>2.096844027485076</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410715</v>
+        <v>3.691568158410714</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-7.677364695466729</v>
+        <v>-8.005118998311211</v>
       </c>
       <c r="E1888" t="n">
-        <v>0.1080203919032403</v>
+        <v>-0.02308132923455242</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.600113572668337</v>
+        <v>-1.581772688861553</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.219254550802678</v>
+        <v>2.230259081086748</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240575</v>
+        <v>3.676837974240574</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-7.47821258822963</v>
+        <v>-7.805966891074112</v>
       </c>
       <c r="E1889" t="n">
-        <v>0.1746301011513967</v>
+        <v>0.04352838001360437</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.434791046718523</v>
+        <v>-1.416450162911739</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.305396932725882</v>
+        <v>2.316401463009953</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-7.548488871256496</v>
+        <v>-7.580121738354701</v>
       </c>
       <c r="E1890" t="n">
-        <v>0.1560986609768586</v>
+        <v>0.1434455141375772</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.465505102933976</v>
+        <v>-1.374523487324576</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.296547572032819</v>
+        <v>2.35113654139846</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282099</v>
+        <v>3.684840248282098</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-7.262214058933802</v>
+        <v>-7.293846926032007</v>
       </c>
       <c r="E1891" t="n">
-        <v>0.2717477304619953</v>
+        <v>0.2590945836227139</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.465505102933976</v>
+        <v>-1.374523487324576</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.297686716588878</v>
+        <v>2.352275685954519</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116214</v>
+        <v>3.710931958116213</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-7.035418231860469</v>
+        <v>-7.067051098958673</v>
       </c>
       <c r="E1892" t="n">
-        <v>0.3650998354534365</v>
+        <v>0.3524466886141551</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.397391158312431</v>
+        <v>-1.306409542703031</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.341188857523913</v>
+        <v>2.395777826889553</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081566</v>
+        <v>3.768948099081565</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-6.75150950093172</v>
+        <v>-6.783142368029924</v>
       </c>
       <c r="E1893" t="n">
-        <v>0.4843970320635727</v>
+        <v>0.4717438852242912</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.397391158312431</v>
+        <v>-1.306409542703031</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.346922561762549</v>
+        <v>2.401511531128189</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425326</v>
+        <v>3.728574354425325</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-6.504522250738767</v>
+        <v>-6.536155117836971</v>
       </c>
       <c r="E1894" t="n">
-        <v>0.5734546697468881</v>
+        <v>0.5608015229076071</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.150403908119479</v>
+        <v>-1.059422292510079</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.485377649484455</v>
+        <v>2.539966618850095</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.74769908470241</v>
+        <v>3.747699084702409</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-6.240685383534698</v>
+        <v>-6.272318250632902</v>
       </c>
       <c r="E1895" t="n">
-        <v>0.6691059353156081</v>
+        <v>0.6564527884763272</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.150403908119479</v>
+        <v>-1.059422292510079</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.475494168171548</v>
+        <v>2.530083137537188</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906227</v>
+        <v>3.766313503906225</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-5.973443582666301</v>
+        <v>-6.005076449764505</v>
       </c>
       <c r="E1896" t="n">
-        <v>0.7741680951635934</v>
+        <v>0.761514948324312</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.150403908119479</v>
+        <v>-1.059422292510079</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.473659607672174</v>
+        <v>2.528248577037814</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781949</v>
+        <v>3.784680945781947</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-5.697634419265817</v>
+        <v>-5.729267286364021</v>
       </c>
       <c r="E1897" t="n">
-        <v>0.8841914455503259</v>
+        <v>0.8715382987110449</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.061384599840746</v>
+        <v>-0.9704029842313459</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.526770877665953</v>
+        <v>2.581359847031593</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567244</v>
+        <v>3.800825778567242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-5.428566831498838</v>
+        <v>-5.460199698597042</v>
       </c>
       <c r="E1898" t="n">
-        <v>0.9924869868026116</v>
+        <v>0.9798338399633302</v>
       </c>
       <c r="F1898" t="n">
-        <v>-0.7923170120737665</v>
+        <v>-0.7013353964643665</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.688879936471634</v>
+        <v>2.743468905837275</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487773</v>
+        <v>3.789307536487772</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-5.164506893176042</v>
+        <v>-5.196139760274246</v>
       </c>
       <c r="E1899" t="n">
-        <v>1.084850645969978</v>
+        <v>1.072197499130696</v>
       </c>
       <c r="F1899" t="n">
-        <v>-0.5282570737509703</v>
+        <v>-0.4372754581415703</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.83405558330356</v>
+        <v>2.8886445526692</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309728</v>
+        <v>3.833249172309726</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-4.457427269671204</v>
+        <v>-4.489060136769408</v>
       </c>
       <c r="E1900" t="n">
-        <v>1.364895461711612</v>
+        <v>1.352242314872331</v>
       </c>
       <c r="F1900" t="n">
-        <v>-0.5282570737509703</v>
+        <v>-0.4372754581415703</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.831268549643259</v>
+        <v>2.885857519008899</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.83937087185873</v>
+        <v>3.839370871858728</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-4.207786239685252</v>
+        <v>-4.239419106783456</v>
       </c>
       <c r="E1901" t="n">
-        <v>1.465095497593834</v>
+        <v>1.452442350754553</v>
       </c>
       <c r="F1901" t="n">
-        <v>-0.2786160437650186</v>
+        <v>-0.1876344281556186</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.981396791522672</v>
+        <v>3.035985760888312</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096475</v>
+        <v>3.856158176096473</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-3.953244340344176</v>
+        <v>-3.98487720744238</v>
       </c>
       <c r="E1902" t="n">
-        <v>1.566279078551021</v>
+        <v>1.55362593171174</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.02407414442394307</v>
+        <v>0.06690747118545692</v>
       </c>
       <c r="G1902" t="n">
-        <v>3.133488752348074</v>
+        <v>3.188077721713714</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.78732685376181</v>
+        <v>3.787326853761808</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-3.719763118114578</v>
+        <v>-3.751395985212782</v>
       </c>
       <c r="E1903" t="n">
-        <v>1.667595996280713</v>
+        <v>1.654942849441432</v>
       </c>
       <c r="F1903" t="n">
-        <v>0.2094070778056555</v>
+        <v>0.3003886934150555</v>
       </c>
       <c r="G1903" t="n">
-        <v>3.281501914523685</v>
+        <v>3.336090883889325</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255786</v>
+        <v>3.801633547255785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-3.540054587970705</v>
+        <v>-3.571687455068909</v>
       </c>
       <c r="E1904" t="n">
-        <v>1.736587198025303</v>
+        <v>1.723934051186022</v>
       </c>
       <c r="F1904" t="n">
-        <v>0.2665785819683516</v>
+        <v>0.3575601975777516</v>
       </c>
       <c r="G1904" t="n">
-        <v>3.312912606708344</v>
+        <v>3.367501576073984</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860428</v>
+        <v>3.763178672860426</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-3.407779114339818</v>
+        <v>-3.439411981438022</v>
       </c>
       <c r="E1905" t="n">
-        <v>1.784864874224685</v>
+        <v>1.772211727385404</v>
       </c>
       <c r="F1905" t="n">
-        <v>0.3988540555992383</v>
+        <v>0.4898356712086382</v>
       </c>
       <c r="G1905" t="n">
-        <v>3.387645377633903</v>
+        <v>3.442234346999543</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575952</v>
+        <v>3.784715218575951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-3.217179439666666</v>
+        <v>-3.24881230676487</v>
       </c>
       <c r="E1906" t="n">
-        <v>1.863919804781583</v>
+        <v>1.851266657942301</v>
       </c>
       <c r="F1906" t="n">
-        <v>0.5894537302723911</v>
+        <v>0.6804353458817911</v>
       </c>
       <c r="G1906" t="n">
-        <v>3.504820243125431</v>
+        <v>3.559409212491071</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430986</v>
+        <v>3.753878996430984</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-2.968179640983085</v>
+        <v>-2.999812508081289</v>
       </c>
       <c r="E1907" t="n">
-        <v>1.976426065478674</v>
+        <v>1.963772918639393</v>
       </c>
       <c r="F1907" t="n">
-        <v>0.8384535289559718</v>
+        <v>0.9294351445653718</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.667126463559238</v>
+        <v>3.721715432924878</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077643</v>
+        <v>3.692928280077641</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-2.776800566122145</v>
+        <v>-2.808433433220349</v>
       </c>
       <c r="E1908" t="n">
-        <v>1.925001765823831</v>
+        <v>1.91234861898455</v>
       </c>
       <c r="F1908" t="n">
-        <v>1.029832603816912</v>
+        <v>1.120814219426312</v>
       </c>
       <c r="G1908" t="n">
-        <v>3.653977978876584</v>
+        <v>3.708566948242224</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457901</v>
+        <v>3.7704190084579</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-2.40657002664204</v>
+        <v>-2.529406137564722</v>
       </c>
       <c r="E1909" t="n">
-        <v>2.121638323492959</v>
+        <v>2.072503879123887</v>
       </c>
       <c r="F1909" t="n">
-        <v>1.029832603816912</v>
+        <v>1.120814219426312</v>
       </c>
       <c r="G1909" t="n">
-        <v>3.70252232075367</v>
+        <v>3.75711129011931</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.368992457256376</v>
+        <v>3.371802471770032</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.773280772463557</v>
+        <v>2.773448426330457</v>
       </c>
       <c r="D1910" t="n">
-        <v>-2.40657002664204</v>
+        <v>-2.529406137564722</v>
       </c>
       <c r="E1910" t="n">
-        <v>2.121638323492959</v>
+        <v>2.072503879123887</v>
       </c>
       <c r="F1910" t="n">
-        <v>1.029832603816912</v>
+        <v>1.120814219426312</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.766344569449925</v>
+        <v>2.766512223316825</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240321.xlsx
+++ b/tame_output/ON/bt/strategyON_20240321.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>49.4%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>69.8%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.5%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.8%</t>
+          <t>-15.5%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.6%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>42.6%</t>
         </is>
       </c>
     </row>
@@ -844,17 +844,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>24.8%</t>
+          <t>25.6%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-66.9%</t>
+          <t>-67.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>103.6%</t>
+          <t>104.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>119.7%</t>
+          <t>120.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-545.0%</t>
+          <t>-552.6%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.8%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-40.7%</t>
+          <t>-41.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-62.2%</t>
+          <t>-61.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>86.0%</t>
+          <t>86.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>497.0%</t>
+          <t>501.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-414.5%</t>
+          <t>-416.8%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>61.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>98.5%</t>
+          <t>98.6%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-218.4%</t>
+          <t>-221.4%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,32 +1150,32 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-31.5%</t>
+          <t>-31.8%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-32.6%</t>
+          <t>-29.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-169.0%</t>
+          <t>-201.0%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-3.3%</t>
+          <t>-5.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>64.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.3%</t>
+          <t>99.4%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-290.3%</t>
+          <t>-297.9%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-25.0%</t>
+          <t>-25.5%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>4.6%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-156.4%</t>
+          <t>-158.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-111.9%</t>
+          <t>-117.1%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>-25.7%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>64.6%</t>
+          <t>50.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>88.0%</t>
+          <t>60.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>99.7%</t>
+          <t>93.9%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1443,15 +1443,15 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2024-03-21</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-174.6%</t>
+          <t>-179.1%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,47 +1466,47 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.5%</t>
+          <t>-21.9%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>-1.4%</t>
+          <t>60.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>41.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-13.6%</t>
+          <t>-15.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-169.4%</t>
+          <t>-104.5%</t>
         </is>
       </c>
     </row>
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.367486348913546</v>
+        <v>-2.44356446520923</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.192197035060217</v>
+        <v>2.161765788541943</v>
       </c>
       <c r="F1854" t="n">
-        <v>0.02149507379798427</v>
+        <v>-0.05458304249769907</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.152445043218174</v>
+        <v>3.106798173440763</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-2.367917047962142</v>
+        <v>-2.443995164257825</v>
       </c>
       <c r="E1855" t="n">
-        <v>2.190567294253642</v>
+        <v>2.160136047735368</v>
       </c>
       <c r="F1855" t="n">
-        <v>0.02149507379798427</v>
+        <v>-0.05458304249769907</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.150987582031037</v>
+        <v>3.105340712253627</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-2.711599821188805</v>
+        <v>-2.787677937484488</v>
       </c>
       <c r="E1856" t="n">
-        <v>2.054863308417593</v>
+        <v>2.024432061899319</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.08641097822923394</v>
+        <v>-0.1624890945249173</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.088013074269322</v>
+        <v>3.042366204491912</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.069250171427153</v>
+        <v>-3.145328287722836</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.907909226978512</v>
+        <v>1.877477980460238</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.4440613284675821</v>
+        <v>-0.5201394447632655</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.869528922782571</v>
+        <v>2.823882053005161</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.075911111649301</v>
+        <v>-3.151989227944984</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.907017777589912</v>
+        <v>1.876586531071638</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.4440613284675821</v>
+        <v>-0.5201394447632655</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.871301849482831</v>
+        <v>2.82565497970542</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-3.507716904799088</v>
+        <v>-3.583795021094772</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.720628347797401</v>
+        <v>1.690197101279128</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.5804788249088491</v>
+        <v>-0.6565569412045325</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.775784239085475</v>
+        <v>2.730137369308065</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-3.834149433666832</v>
+        <v>-3.910227549962515</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.578340111252394</v>
+        <v>1.547908864734121</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.6629470754159972</v>
+        <v>-0.7390251917116806</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.714588063783276</v>
+        <v>2.668941194005866</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-3.835713584777135</v>
+        <v>-3.911791701072818</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.576295042464238</v>
+        <v>1.545863795945965</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.6629470754159972</v>
+        <v>-0.7390251917116806</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.713168655439242</v>
+        <v>2.667521785661831</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-4.199339829677448</v>
+        <v>-4.275417945973132</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.437332104738355</v>
+        <v>1.406900858220081</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.761168712283123</v>
+        <v>-0.8372468285788064</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.660723233553208</v>
+        <v>2.615076363775798</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-4.196912765148729</v>
+        <v>-4.272990881444414</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.437557445555674</v>
+        <v>1.4071261990374</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.7615014940902747</v>
+        <v>-0.8375796103859581</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.659778079474748</v>
+        <v>2.614131209697338</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-4.605501542329408</v>
+        <v>-4.681579658625092</v>
       </c>
       <c r="E1864" t="n">
-        <v>1.272883478698161</v>
+        <v>1.242452232179888</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.170090271270953</v>
+        <v>-1.246168387566637</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.4133863571811</v>
+        <v>2.36773948740369</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-5.018484026470502</v>
+        <v>-5.094562142766185</v>
       </c>
       <c r="E1865" t="n">
-        <v>1.102875917513184</v>
+        <v>1.072444670994911</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.170090271270953</v>
+        <v>-1.246168387566637</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.40857178965256</v>
+        <v>2.362924919875151</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-5.4348759007575</v>
+        <v>-5.510954017053183</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.9343132184072624</v>
+        <v>0.9038819718889894</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.170090271270953</v>
+        <v>-1.246168387566637</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.406565840261438</v>
+        <v>2.360918970484028</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-5.811552911287344</v>
+        <v>-5.887631027583027</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.7939011048640037</v>
+        <v>0.7634698583457307</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.170090271270953</v>
+        <v>-1.246168387566637</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.416824530930117</v>
+        <v>2.371177661152707</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-5.825267775612455</v>
+        <v>-5.901345891908139</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.7845147242796546</v>
+        <v>0.7540834777613812</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.170090271270953</v>
+        <v>-1.246168387566637</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.412924096075812</v>
+        <v>2.367277226298402</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.138092574857435</v>
+        <v>-6.214170691153118</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.6577897246366633</v>
+        <v>0.6273584781183903</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.170090271270953</v>
+        <v>-1.246168387566637</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.411329016130813</v>
+        <v>2.365682146353403</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-6.142905613322772</v>
+        <v>-6.218983729618455</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.6596434851797368</v>
+        <v>0.6292122386614634</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.171636905973739</v>
+        <v>-1.247715022269422</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.41418001123835</v>
+        <v>2.36853314146094</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-6.576254721433008</v>
+        <v>-6.652332837728691</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.4822775374012394</v>
+        <v>0.4518462908829659</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.171636905973739</v>
+        <v>-1.247715022269422</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.410153706703947</v>
+        <v>2.364506836926537</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-6.959256110175639</v>
+        <v>-7.035334226471322</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.3289748805826029</v>
+        <v>0.2985436340643295</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.171636905973739</v>
+        <v>-1.247715022269422</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.410051605382363</v>
+        <v>2.364404735604953</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.334241436346916</v>
+        <v>-7.4103195526426</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.181552266085522</v>
+        <v>0.1511210195672485</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.546622232145016</v>
+        <v>-1.6227003484407</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.187631925651027</v>
+        <v>2.141985055873616</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-7.693771758850918</v>
+        <v>-7.769849875146601</v>
       </c>
       <c r="E1874" t="n">
-        <v>0.04309044038197163</v>
+        <v>0.01265919386369818</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.546622232145016</v>
+        <v>-1.6227003484407</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.192982228949076</v>
+        <v>2.147335359171667</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.020171787515931</v>
+        <v>-8.096249903811614</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.07955355112685636</v>
+        <v>-0.1099847976451294</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.873022260810029</v>
+        <v>-1.949100377105712</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.005058231707246</v>
+        <v>1.959411361929837</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.013695640722371</v>
+        <v>-8.089773757018055</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.07392134178766341</v>
+        <v>-0.1043525883059369</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.86654611401647</v>
+        <v>-1.942624230312153</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.011985670405151</v>
+        <v>1.966338800627741</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.010004715765961</v>
+        <v>-8.086082832061644</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.07244497180509901</v>
+        <v>-0.1028762183233725</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.86654611401647</v>
+        <v>-1.942624230312153</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.011985670405151</v>
+        <v>1.966338800627741</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.002789362894145</v>
+        <v>-8.078867479189828</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.06404563353773041</v>
+        <v>-0.09447688005600385</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.796767878726088</v>
+        <v>-1.872845995021771</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.059365808698022</v>
+        <v>2.013718938920612</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-7.951761516812319</v>
+        <v>-8.027839633108002</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.03915194062056404</v>
+        <v>-0.06958318713883704</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.721558540418987</v>
+        <v>-1.79763665671467</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.108973966166719</v>
+        <v>2.063327096389309</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-7.878291685144871</v>
+        <v>-7.954369801440554</v>
       </c>
       <c r="E1880" t="n">
-        <v>0.005607693539836589</v>
+        <v>-0.02482355297843686</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.648088708751538</v>
+        <v>-1.724166825047222</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.168427566660609</v>
+        <v>2.1227806968832</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-7.797919329680941</v>
+        <v>-7.873997445976624</v>
       </c>
       <c r="E1881" t="n">
-        <v>0.05231185647292502</v>
+        <v>0.02188060995465202</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.567716353287609</v>
+        <v>-1.643794469583292</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.231206200686484</v>
+        <v>2.185559330909074</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-7.986192132046785</v>
+        <v>-8.062270248342468</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.03021642937500868</v>
+        <v>-0.06064767589328168</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.567716353287609</v>
+        <v>-1.643794469583292</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.223987035784888</v>
+        <v>2.178340166007478</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-8.006356773596332</v>
+        <v>-8.082434889892015</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.04495447676880371</v>
+        <v>-0.07538572328707671</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.587880994837156</v>
+        <v>-1.663959111132839</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.205216060081183</v>
+        <v>2.159569190303773</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-8.236181220760157</v>
+        <v>-8.31225933705584</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.1357684657957772</v>
+        <v>-0.1661997123140506</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.750528531907316</v>
+        <v>-1.826606648203</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.108743327677643</v>
+        <v>2.063096457900233</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-8.173111988453817</v>
+        <v>-8.2491901047495</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.1078470442441266</v>
+        <v>-0.1382782907624001</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.779042094589551</v>
+        <v>-1.855120210885234</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.094328918697418</v>
+        <v>2.048682048920007</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-8.121096474485004</v>
+        <v>-8.197174590780687</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.08305050297020067</v>
+        <v>-0.1134817494884737</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.779042094589551</v>
+        <v>-1.855120210885234</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.098319254383818</v>
+        <v>2.052672384606408</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-8.202388404039208</v>
+        <v>-8.278466520334891</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.1170425016906238</v>
+        <v>-0.1474737482088972</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.779042094589551</v>
+        <v>-1.855120210885234</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.096844027485076</v>
+        <v>2.051197157707667</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-8.005118998311211</v>
+        <v>-8.081197114606894</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.02308132923455242</v>
+        <v>-0.05351257575282586</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.581772688861553</v>
+        <v>-1.657850805157236</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.230259081086748</v>
+        <v>2.184612211309338</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-7.805966891074112</v>
+        <v>-7.882045007369795</v>
       </c>
       <c r="E1889" t="n">
-        <v>0.04352838001360437</v>
+        <v>0.01309713349533048</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.416450162911739</v>
+        <v>-1.492528279207423</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.316401463009953</v>
+        <v>2.270754593232543</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-7.580121738354701</v>
+        <v>-7.656199854650384</v>
       </c>
       <c r="E1890" t="n">
-        <v>0.1434455141375772</v>
+        <v>0.1130142676193038</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.374523487324576</v>
+        <v>-1.450601603620259</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.35113654139846</v>
+        <v>2.30548967162105</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-7.293846926032007</v>
+        <v>-7.36992504232769</v>
       </c>
       <c r="E1891" t="n">
-        <v>0.2590945836227139</v>
+        <v>0.22866333710444</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.374523487324576</v>
+        <v>-1.450601603620259</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.352275685954519</v>
+        <v>2.306628816177108</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-7.067051098958673</v>
+        <v>-7.143129215254357</v>
       </c>
       <c r="E1892" t="n">
-        <v>0.3524466886141551</v>
+        <v>0.3220154420958812</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.306409542703031</v>
+        <v>-1.382487658998715</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.395777826889553</v>
+        <v>2.350130957112143</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-6.783142368029924</v>
+        <v>-6.859220484325608</v>
       </c>
       <c r="E1893" t="n">
-        <v>0.4717438852242912</v>
+        <v>0.4413126387060173</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.306409542703031</v>
+        <v>-1.382487658998715</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.401511531128189</v>
+        <v>2.355864661350779</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-6.536155117836971</v>
+        <v>-6.612233234132655</v>
       </c>
       <c r="E1894" t="n">
-        <v>0.5608015229076071</v>
+        <v>0.5303702763893332</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.059422292510079</v>
+        <v>-1.135500408805763</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.539966618850095</v>
+        <v>2.494319749072685</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-6.272318250632902</v>
+        <v>-6.348396366928586</v>
       </c>
       <c r="E1895" t="n">
-        <v>0.6564527884763272</v>
+        <v>0.6260215419580528</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.059422292510079</v>
+        <v>-1.135500408805763</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.530083137537188</v>
+        <v>2.484436267759778</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-6.005076449764505</v>
+        <v>-6.08115456606019</v>
       </c>
       <c r="E1896" t="n">
-        <v>0.761514948324312</v>
+        <v>0.7310837018060381</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.059422292510079</v>
+        <v>-1.135500408805763</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.528248577037814</v>
+        <v>2.482601707260404</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-5.729267286364021</v>
+        <v>-5.805345402659706</v>
       </c>
       <c r="E1897" t="n">
-        <v>0.8715382987110449</v>
+        <v>0.841107052192771</v>
       </c>
       <c r="F1897" t="n">
-        <v>-0.9704029842313459</v>
+        <v>-1.046481100527029</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.581359847031593</v>
+        <v>2.535712977254184</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-5.460199698597042</v>
+        <v>-5.536277814892726</v>
       </c>
       <c r="E1898" t="n">
-        <v>0.9798338399633302</v>
+        <v>0.9494025934450563</v>
       </c>
       <c r="F1898" t="n">
-        <v>-0.7013353964643665</v>
+        <v>-0.7774135127600496</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.743468905837275</v>
+        <v>2.697822036059864</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-5.196139760274246</v>
+        <v>-5.27221787656993</v>
       </c>
       <c r="E1899" t="n">
-        <v>1.072197499130696</v>
+        <v>1.041766252612423</v>
       </c>
       <c r="F1899" t="n">
-        <v>-0.4372754581415703</v>
+        <v>-0.5133535744372534</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.8886445526692</v>
+        <v>2.84299768289179</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-4.489060136769408</v>
+        <v>-4.565138253065092</v>
       </c>
       <c r="E1900" t="n">
-        <v>1.352242314872331</v>
+        <v>1.321811068354057</v>
       </c>
       <c r="F1900" t="n">
-        <v>-0.4372754581415703</v>
+        <v>-0.5133535744372534</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.885857519008899</v>
+        <v>2.840210649231489</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-4.239419106783456</v>
+        <v>-4.31549722307914</v>
       </c>
       <c r="E1901" t="n">
-        <v>1.452442350754553</v>
+        <v>1.422011104236279</v>
       </c>
       <c r="F1901" t="n">
-        <v>-0.1876344281556186</v>
+        <v>-0.2637125444513017</v>
       </c>
       <c r="G1901" t="n">
-        <v>3.035985760888312</v>
+        <v>2.990338891110901</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-3.98487720744238</v>
+        <v>-4.060955323738064</v>
       </c>
       <c r="E1902" t="n">
-        <v>1.55362593171174</v>
+        <v>1.523194685193467</v>
       </c>
       <c r="F1902" t="n">
-        <v>0.06690747118545692</v>
+        <v>-0.009170645110226139</v>
       </c>
       <c r="G1902" t="n">
-        <v>3.188077721713714</v>
+        <v>3.142430851936304</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-3.751395985212782</v>
+        <v>-3.827474101508465</v>
       </c>
       <c r="E1903" t="n">
-        <v>1.654942849441432</v>
+        <v>1.624511602923158</v>
       </c>
       <c r="F1903" t="n">
-        <v>0.3003886934150555</v>
+        <v>0.2243105771193724</v>
       </c>
       <c r="G1903" t="n">
-        <v>3.336090883889325</v>
+        <v>3.290444014111916</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-3.571687455068909</v>
+        <v>-3.647765571364593</v>
       </c>
       <c r="E1904" t="n">
-        <v>1.723934051186022</v>
+        <v>1.693502804667748</v>
       </c>
       <c r="F1904" t="n">
-        <v>0.3575601975777516</v>
+        <v>0.2814820812820685</v>
       </c>
       <c r="G1904" t="n">
-        <v>3.367501576073984</v>
+        <v>3.321854706296574</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-3.439411981438022</v>
+        <v>-3.515490097733706</v>
       </c>
       <c r="E1905" t="n">
-        <v>1.772211727385404</v>
+        <v>1.74178048086713</v>
       </c>
       <c r="F1905" t="n">
-        <v>0.4898356712086382</v>
+        <v>0.4137575549129552</v>
       </c>
       <c r="G1905" t="n">
-        <v>3.442234346999543</v>
+        <v>3.396587477222133</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-3.24881230676487</v>
+        <v>-3.324890423060554</v>
       </c>
       <c r="E1906" t="n">
-        <v>1.851266657942301</v>
+        <v>1.820835411424027</v>
       </c>
       <c r="F1906" t="n">
-        <v>0.6804353458817911</v>
+        <v>0.604357229586108</v>
       </c>
       <c r="G1906" t="n">
-        <v>3.559409212491071</v>
+        <v>3.513762342713661</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-2.999812508081289</v>
+        <v>-3.075890624376973</v>
       </c>
       <c r="E1907" t="n">
-        <v>1.963772918639393</v>
+        <v>1.933341672121118</v>
       </c>
       <c r="F1907" t="n">
-        <v>0.9294351445653718</v>
+        <v>0.8533570282696887</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.721715432924878</v>
+        <v>3.676068563147469</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-2.808433433220349</v>
+        <v>-2.884511549516033</v>
       </c>
       <c r="E1908" t="n">
-        <v>1.91234861898455</v>
+        <v>1.881917372466276</v>
       </c>
       <c r="F1908" t="n">
-        <v>1.120814219426312</v>
+        <v>1.044736103130629</v>
       </c>
       <c r="G1908" t="n">
-        <v>3.708566948242224</v>
+        <v>3.662920078464814</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-2.529406137564722</v>
+        <v>-2.605484253860406</v>
       </c>
       <c r="E1909" t="n">
-        <v>2.072503879123887</v>
+        <v>2.042072632605613</v>
       </c>
       <c r="F1909" t="n">
-        <v>1.120814219426312</v>
+        <v>1.044736103130629</v>
       </c>
       <c r="G1909" t="n">
-        <v>3.75711129011931</v>
+        <v>3.7114644203419</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.371802471770032</v>
+        <v>3.706408888204881</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.773448426330457</v>
+        <v>2.773495992160886</v>
       </c>
       <c r="D1910" t="n">
-        <v>-2.529406137564722</v>
+        <v>-2.55222190269158</v>
       </c>
       <c r="E1910" t="n">
-        <v>2.072503879123887</v>
+        <v>1.752250806770507</v>
       </c>
       <c r="F1910" t="n">
-        <v>1.120814219426312</v>
+        <v>1.068941436755595</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.766512223316825</v>
+        <v>3.414860854214244</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240321.xlsx
+++ b/tame_output/ON/bt/strategyON_20240321.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>50.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.5%</t>
+          <t>-17.8%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-12.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>11.7%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>61.0%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-39.3%</t>
+          <t>-39.1%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -844,17 +844,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>25.6%</t>
+          <t>24.9%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-34.3%</t>
+          <t>-34.1%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-67.4%</t>
+          <t>-66.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>104.2%</t>
+          <t>103.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>120.8%</t>
+          <t>119.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>86.5%</t>
+          <t>86.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-552.6%</t>
+          <t>-539.1%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-41.0%</t>
+          <t>-40.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-61.9%</t>
+          <t>-60.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>86.4%</t>
+          <t>85.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1022,17 +1022,17 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>501.8%</t>
+          <t>497.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-416.8%</t>
+          <t>-412.3%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>22.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>50.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>61.8%</t>
+          <t>59.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>42.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>98.6%</t>
+          <t>98.5%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-221.4%</t>
+          <t>-216.0%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-31.8%</t>
+          <t>-31.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>42.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-29.1%</t>
+          <t>-36.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-201.0%</t>
+          <t>-199.1%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-5.2%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>64.6%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>70.1%</t>
+          <t>71.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.4%</t>
+          <t>99.2%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-297.9%</t>
+          <t>-281.3%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-25.5%</t>
+          <t>-24.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,32 +1323,32 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-158.6%</t>
+          <t>-152.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-117.1%</t>
+          <t>-84.7%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>75.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>50.2%</t>
+          <t>48.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.9%</t>
+          <t>58.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>93.9%</t>
+          <t>93.2%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-179.1%</t>
+          <t>-169.2%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.9%</t>
+          <t>-21.0%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>60.7%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>41.9%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.8%</t>
+          <t>-15.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-104.5%</t>
+          <t>-85.0%</t>
         </is>
       </c>
     </row>
@@ -44164,22 +44164,22 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416044</v>
+        <v>3.231167537416045</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.000775297247001</v>
+        <v>-1.564851314374194</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.337775063683103</v>
+        <v>2.512144656832226</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.3882061254645299</v>
+        <v>0.4780349216860705</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.371365282174369</v>
+        <v>3.425262559907293</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.44356446520923</v>
+        <v>-1.931562366040739</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.161765788541943</v>
+        <v>2.366566628209339</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.05458304249769907</v>
+        <v>0.1113238700195249</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.106798173440763</v>
+        <v>3.206342320951098</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-2.443995164257825</v>
+        <v>-2.30904638824813</v>
       </c>
       <c r="E1855" t="n">
-        <v>2.160136047735368</v>
+        <v>2.214115558139246</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.05458304249769907</v>
+        <v>0.1113238700195249</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.105340712253627</v>
+        <v>3.204884859763961</v>
       </c>
     </row>
     <row r="1856">
@@ -44233,22 +44233,22 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347055</v>
+        <v>3.299136146347056</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-2.787677937484488</v>
+        <v>-2.652729161474793</v>
       </c>
       <c r="E1856" t="n">
-        <v>2.024432061899319</v>
+        <v>2.078411572303198</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.1624890945249173</v>
+        <v>0.003417817992306726</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.042366204491912</v>
+        <v>3.141910352002246</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.145328287722836</v>
+        <v>-3.010379511713141</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.877477980460238</v>
+        <v>1.931457490864116</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.5201394447632655</v>
+        <v>-0.3542325322460414</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.823882053005161</v>
+        <v>2.923426200515495</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.151989227944984</v>
+        <v>-3.017040451935288</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.876586531071638</v>
+        <v>1.930566041475517</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.5201394447632655</v>
+        <v>-0.3542325322460414</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.82565497970542</v>
+        <v>2.925199127215755</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-3.583795021094772</v>
+        <v>-3.448846245085076</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.690197101279128</v>
+        <v>1.744176611683006</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.6565569412045325</v>
+        <v>-0.4906500286873084</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.730137369308065</v>
+        <v>2.829681516818399</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-3.910227549962515</v>
+        <v>-3.77527877395282</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.547908864734121</v>
+        <v>1.601888375137999</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.7390251917116806</v>
+        <v>-0.5731182791944566</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.668941194005866</v>
+        <v>2.768485341516201</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-3.911791701072818</v>
+        <v>-3.776842925063123</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.545863795945965</v>
+        <v>1.599843306349843</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.7390251917116806</v>
+        <v>-0.5731182791944566</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.667521785661831</v>
+        <v>2.767065933172166</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-4.275417945973132</v>
+        <v>-4.140469169963436</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.406900858220081</v>
+        <v>1.46088036862396</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.8372468285788064</v>
+        <v>-0.6713399160615824</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.615076363775798</v>
+        <v>2.714620511286132</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-4.272990881444414</v>
+        <v>-4.138042105434717</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.4071261990374</v>
+        <v>1.461105709441278</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.8375796103859581</v>
+        <v>-0.671672697868734</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.614131209697338</v>
+        <v>2.713675357207673</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-4.681579658625092</v>
+        <v>-4.546630882615396</v>
       </c>
       <c r="E1864" t="n">
-        <v>1.242452232179888</v>
+        <v>1.296431742583766</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.246168387566637</v>
+        <v>-1.080261475049412</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.36773948740369</v>
+        <v>2.467283634914025</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-5.094562142766185</v>
+        <v>-4.95961336675649</v>
       </c>
       <c r="E1865" t="n">
-        <v>1.072444670994911</v>
+        <v>1.126424181398789</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.246168387566637</v>
+        <v>-1.080261475049412</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.362924919875151</v>
+        <v>2.462469067385485</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-5.510954017053183</v>
+        <v>-5.376005241043488</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.9038819718889894</v>
+        <v>0.9578614822928673</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.246168387566637</v>
+        <v>-1.080261475049412</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.360918970484028</v>
+        <v>2.460463117994363</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-5.887631027583027</v>
+        <v>-5.752682251573332</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.7634698583457307</v>
+        <v>0.8174493687496085</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.246168387566637</v>
+        <v>-1.080261475049412</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.371177661152707</v>
+        <v>2.470721808663042</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-5.901345891908139</v>
+        <v>-5.766397115898443</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.7540834777613812</v>
+        <v>0.8080629881652595</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.246168387566637</v>
+        <v>-1.080261475049412</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.367277226298402</v>
+        <v>2.466821373808737</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.214170691153118</v>
+        <v>-6.079221915143423</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.6273584781183903</v>
+        <v>0.6813379885222681</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.246168387566637</v>
+        <v>-1.080261475049412</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.365682146353403</v>
+        <v>2.465226293863738</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-6.218983729618455</v>
+        <v>-6.08403495360876</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.6292122386614634</v>
+        <v>0.6831917490653416</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.247715022269422</v>
+        <v>-1.081808109752198</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.36853314146094</v>
+        <v>2.468077288971275</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.41997943392309</v>
+        <v>3.419979433923089</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-6.652332837728691</v>
+        <v>-6.517384061718996</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.4518462908829659</v>
+        <v>0.5058258012868442</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.247715022269422</v>
+        <v>-1.081808109752198</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.364506836926537</v>
+        <v>2.464050984436871</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297752</v>
+        <v>3.458100091297751</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.035334226471322</v>
+        <v>-6.900385450461627</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.2985436340643295</v>
+        <v>0.3525231444682078</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.247715022269422</v>
+        <v>-1.081808109752198</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.364404735604953</v>
+        <v>2.463948883115287</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317618</v>
+        <v>3.447750501317617</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.4103195526426</v>
+        <v>-7.275370776632904</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.1511210195672485</v>
+        <v>0.2051005299711268</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.6227003484407</v>
+        <v>-1.456793435923476</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.141985055873616</v>
+        <v>2.241529203383951</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-7.769849875146601</v>
+        <v>-7.634901099136906</v>
       </c>
       <c r="E1874" t="n">
-        <v>0.01265919386369818</v>
+        <v>0.06663870426757645</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.6227003484407</v>
+        <v>-1.456793435923476</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.147335359171667</v>
+        <v>2.246879506682001</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341315</v>
+        <v>3.503170282341314</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.096249903811614</v>
+        <v>-7.961301127801919</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.1099847976451294</v>
+        <v>-0.05600528724125153</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.949100377105712</v>
+        <v>-1.783193464588488</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.959411361929837</v>
+        <v>2.058955509440171</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776678</v>
+        <v>3.500446096776677</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.089773757018055</v>
+        <v>-7.954824981008359</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.1043525883059369</v>
+        <v>-0.05037307790205858</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.942624230312153</v>
+        <v>-1.776717317794929</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.966338800627741</v>
+        <v>2.065882948138076</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407493</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.086082832061644</v>
+        <v>-7.951134056051948</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.1028762183233725</v>
+        <v>-0.04889670791949419</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.942624230312153</v>
+        <v>-1.776717317794929</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.966338800627741</v>
+        <v>2.065882948138076</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611697</v>
+        <v>3.502786823611695</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.078867479189828</v>
+        <v>-7.943918703180132</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.09447688005600385</v>
+        <v>-0.04049736965212514</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.872845995021771</v>
+        <v>-1.706939082504547</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.013718938920612</v>
+        <v>2.113263086430947</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199886</v>
+        <v>3.496848329199885</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.027839633108002</v>
+        <v>-7.892890857098306</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.06958318713883704</v>
+        <v>-0.01560367673495877</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.79763665671467</v>
+        <v>-1.631729744197446</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.063327096389309</v>
+        <v>2.162871243899644</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910629</v>
+        <v>3.499968163910628</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-7.954369801440554</v>
+        <v>-7.819421025430858</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.02482355297843686</v>
+        <v>0.02915595742544141</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.724166825047222</v>
+        <v>-1.558259912529997</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.1227806968832</v>
+        <v>2.222324844393534</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078597</v>
+        <v>3.490055666078595</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-7.873997445976624</v>
+        <v>-7.739048669966928</v>
       </c>
       <c r="E1881" t="n">
-        <v>0.02188060995465202</v>
+        <v>0.07586012035853029</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.643794469583292</v>
+        <v>-1.477887557066068</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.185559330909074</v>
+        <v>2.285103478419408</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880268</v>
+        <v>3.485875018880266</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.062270248342468</v>
+        <v>-7.927321472332772</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.06064767589328168</v>
+        <v>-0.00666816548940341</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.643794469583292</v>
+        <v>-1.477887557066068</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.178340166007478</v>
+        <v>2.277884313517812</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234393</v>
+        <v>3.480688917234391</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-8.082434889892015</v>
+        <v>-7.947486113882319</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.07538572328707671</v>
+        <v>-0.02140621288319844</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.663959111132839</v>
+        <v>-1.498052198615615</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.159569190303773</v>
+        <v>2.259113337814108</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860582</v>
+        <v>3.493712438860581</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-8.31225933705584</v>
+        <v>-8.177310561046145</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.1661997123140506</v>
+        <v>-0.1122202019101723</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.826606648203</v>
+        <v>-1.660699735685776</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.063096457900233</v>
+        <v>2.162640605410568</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767396</v>
+        <v>3.492098065767394</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-8.2491901047495</v>
+        <v>-8.114241328739805</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.1382782907624001</v>
+        <v>-0.08429878035852179</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.855120210885234</v>
+        <v>-1.68921329836801</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.048682048920007</v>
+        <v>2.148226196430342</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.57367044979254</v>
+        <v>3.573670449792538</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-8.197174590780687</v>
+        <v>-8.062225814770992</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.1134817494884737</v>
+        <v>-0.05950223908459584</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.855120210885234</v>
+        <v>-1.68921329836801</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.052672384606408</v>
+        <v>2.152216532116743</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628917</v>
+        <v>3.600034689628915</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-8.278466520334891</v>
+        <v>-8.143517744325196</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.1474737482088972</v>
+        <v>-0.09349423780501898</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.855120210885234</v>
+        <v>-1.68921329836801</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.051197157707667</v>
+        <v>2.150741305218001</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410714</v>
+        <v>3.691568158410712</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-8.081197114606894</v>
+        <v>-7.946248338597198</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.05351257575282586</v>
+        <v>0.0004669346510524086</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.657850805157236</v>
+        <v>-1.491943892640012</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.184612211309338</v>
+        <v>2.284156358819672</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240574</v>
+        <v>3.676837974240573</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-7.882045007369795</v>
+        <v>-7.747096231360099</v>
       </c>
       <c r="E1889" t="n">
-        <v>0.01309713349533048</v>
+        <v>0.0670766438992092</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.492528279207423</v>
+        <v>-1.326621366690198</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.270754593232543</v>
+        <v>2.370298740742877</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085277</v>
+        <v>3.685157806085275</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-7.656199854650384</v>
+        <v>-7.521251078640688</v>
       </c>
       <c r="E1890" t="n">
-        <v>0.1130142676193038</v>
+        <v>0.166993778023182</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.450601603620259</v>
+        <v>-1.284694691103035</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.30548967162105</v>
+        <v>2.405033819131384</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282098</v>
+        <v>3.684840248282097</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-7.36992504232769</v>
+        <v>-7.536633618470312</v>
       </c>
       <c r="E1891" t="n">
-        <v>0.22866333710444</v>
+        <v>0.1619799066473915</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.450601603620259</v>
+        <v>-1.284694691103035</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.306628816177108</v>
+        <v>2.406172963687443</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116213</v>
+        <v>3.710931958116212</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-7.143129215254357</v>
+        <v>-7.309837791396978</v>
       </c>
       <c r="E1892" t="n">
-        <v>0.3220154420958812</v>
+        <v>0.2553320116388327</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.382487658998715</v>
+        <v>-1.21658074648149</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.350130957112143</v>
+        <v>2.449675104622477</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081565</v>
+        <v>3.768948099081563</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-6.859220484325608</v>
+        <v>-7.025929060468229</v>
       </c>
       <c r="E1893" t="n">
-        <v>0.4413126387060173</v>
+        <v>0.3746292082489688</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.382487658998715</v>
+        <v>-1.21658074648149</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.355864661350779</v>
+        <v>2.455408808861114</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425325</v>
+        <v>3.728574354425323</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-6.612233234132655</v>
+        <v>-6.778941810275277</v>
       </c>
       <c r="E1894" t="n">
-        <v>0.5303702763893332</v>
+        <v>0.4636868459322843</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.135500408805763</v>
+        <v>-0.9695934962885383</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.494319749072685</v>
+        <v>2.59386389658302</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702409</v>
+        <v>3.747699084702408</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-6.348396366928586</v>
+        <v>-6.515104943071208</v>
       </c>
       <c r="E1895" t="n">
-        <v>0.6260215419580528</v>
+        <v>0.5593381115010043</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.135500408805763</v>
+        <v>-0.9695934962885383</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.484436267759778</v>
+        <v>2.583980415270112</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906225</v>
+        <v>3.766313503906224</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-6.08115456606019</v>
+        <v>-6.247863142202811</v>
       </c>
       <c r="E1896" t="n">
-        <v>0.7310837018060381</v>
+        <v>0.6644002713489896</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.135500408805763</v>
+        <v>-0.9695934962885383</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.482601707260404</v>
+        <v>2.582145854770738</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781947</v>
+        <v>3.784680945781945</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-5.805345402659706</v>
+        <v>-5.972053978802327</v>
       </c>
       <c r="E1897" t="n">
-        <v>0.841107052192771</v>
+        <v>0.7744236217357221</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.046481100527029</v>
+        <v>-0.8805741880098048</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.535712977254184</v>
+        <v>2.635257124764518</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567242</v>
+        <v>3.800825778567241</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-5.536277814892726</v>
+        <v>-5.702986391035347</v>
       </c>
       <c r="E1898" t="n">
-        <v>0.9494025934450563</v>
+        <v>0.8827191629880078</v>
       </c>
       <c r="F1898" t="n">
-        <v>-0.7774135127600496</v>
+        <v>-0.6115066002428254</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.697822036059864</v>
+        <v>2.797366183570199</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487772</v>
+        <v>3.78930753648777</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-5.27221787656993</v>
+        <v>-5.438926452712551</v>
       </c>
       <c r="E1899" t="n">
-        <v>1.041766252612423</v>
+        <v>0.975082822155374</v>
       </c>
       <c r="F1899" t="n">
-        <v>-0.5133535744372534</v>
+        <v>-0.3474466619200293</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.84299768289179</v>
+        <v>2.942541830402125</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309726</v>
+        <v>3.833249172309723</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-4.565138253065092</v>
+        <v>-4.731846829207713</v>
       </c>
       <c r="E1900" t="n">
-        <v>1.321811068354057</v>
+        <v>1.255127637897008</v>
       </c>
       <c r="F1900" t="n">
-        <v>-0.5133535744372534</v>
+        <v>-0.3474466619200293</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.840210649231489</v>
+        <v>2.939754796741824</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858728</v>
+        <v>3.839370871858725</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-4.31549722307914</v>
+        <v>-4.482205799221761</v>
       </c>
       <c r="E1901" t="n">
-        <v>1.422011104236279</v>
+        <v>1.355327673779231</v>
       </c>
       <c r="F1901" t="n">
-        <v>-0.2637125444513017</v>
+        <v>-0.09780563193407754</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.990338891110901</v>
+        <v>3.089883038621236</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096473</v>
+        <v>3.85615817609647</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-4.060955323738064</v>
+        <v>-4.227663899880685</v>
       </c>
       <c r="E1902" t="n">
-        <v>1.523194685193467</v>
+        <v>1.456511254736418</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.009170645110226139</v>
+        <v>0.156736267406998</v>
       </c>
       <c r="G1902" t="n">
-        <v>3.142430851936304</v>
+        <v>3.241974999446638</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761808</v>
+        <v>3.787326853761805</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-3.827474101508465</v>
+        <v>-3.994182677651087</v>
       </c>
       <c r="E1903" t="n">
-        <v>1.624511602923158</v>
+        <v>1.55782817246611</v>
       </c>
       <c r="F1903" t="n">
-        <v>0.2243105771193724</v>
+        <v>0.3902174896365965</v>
       </c>
       <c r="G1903" t="n">
-        <v>3.290444014111916</v>
+        <v>3.38998816162225</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255785</v>
+        <v>3.801633547255781</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-3.647765571364593</v>
+        <v>-3.814474147507214</v>
       </c>
       <c r="E1904" t="n">
-        <v>1.693502804667748</v>
+        <v>1.6268193742107</v>
       </c>
       <c r="F1904" t="n">
-        <v>0.2814820812820685</v>
+        <v>0.4473889937992926</v>
       </c>
       <c r="G1904" t="n">
-        <v>3.321854706296574</v>
+        <v>3.421398853806908</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860426</v>
+        <v>3.763178672860422</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-3.515490097733706</v>
+        <v>-3.682198673876328</v>
       </c>
       <c r="E1905" t="n">
-        <v>1.74178048086713</v>
+        <v>1.675097050410081</v>
       </c>
       <c r="F1905" t="n">
-        <v>0.4137575549129552</v>
+        <v>0.5796644674301793</v>
       </c>
       <c r="G1905" t="n">
-        <v>3.396587477222133</v>
+        <v>3.496131624732467</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575951</v>
+        <v>3.784715218575947</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-3.324890423060554</v>
+        <v>-3.491598999203175</v>
       </c>
       <c r="E1906" t="n">
-        <v>1.820835411424027</v>
+        <v>1.754151980966979</v>
       </c>
       <c r="F1906" t="n">
-        <v>0.604357229586108</v>
+        <v>0.7702641421033322</v>
       </c>
       <c r="G1906" t="n">
-        <v>3.513762342713661</v>
+        <v>3.613306490223996</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430984</v>
+        <v>3.753878996430981</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-3.075890624376973</v>
+        <v>-3.242599200519594</v>
       </c>
       <c r="E1907" t="n">
-        <v>1.933341672121118</v>
+        <v>1.86665824166407</v>
       </c>
       <c r="F1907" t="n">
-        <v>0.8533570282696887</v>
+        <v>1.019263940786913</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.676068563147469</v>
+        <v>3.775612710657803</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077641</v>
+        <v>3.692928280077638</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-2.884511549516033</v>
+        <v>-3.051220125658654</v>
       </c>
       <c r="E1908" t="n">
-        <v>1.881917372466276</v>
+        <v>1.815233942009227</v>
       </c>
       <c r="F1908" t="n">
-        <v>1.044736103130629</v>
+        <v>1.210643015647853</v>
       </c>
       <c r="G1908" t="n">
-        <v>3.662920078464814</v>
+        <v>3.762464225975148</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.7704190084579</v>
+        <v>3.770419008457896</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-2.605484253860406</v>
+        <v>-2.772192830003028</v>
       </c>
       <c r="E1909" t="n">
-        <v>2.042072632605613</v>
+        <v>1.975389202148564</v>
       </c>
       <c r="F1909" t="n">
-        <v>1.044736103130629</v>
+        <v>1.210643015647853</v>
       </c>
       <c r="G1909" t="n">
-        <v>3.7114644203419</v>
+        <v>3.811008567852235</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.706408888204881</v>
+        <v>3.397886547764343</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.773495992160886</v>
+        <v>2.774948159262315</v>
       </c>
       <c r="D1910" t="n">
-        <v>-2.55222190269158</v>
+        <v>-2.50750517520132</v>
       </c>
       <c r="E1910" t="n">
-        <v>1.752250806770507</v>
+        <v>1.77158966486804</v>
       </c>
       <c r="F1910" t="n">
-        <v>1.068941436755595</v>
+        <v>1.392575697868281</v>
       </c>
       <c r="G1910" t="n">
-        <v>3.414860854214244</v>
+        <v>3.610493577983284</v>
       </c>
     </row>
   </sheetData>
